--- a/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
+++ b/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/C9860F92A834CAE8/Belgeler/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaankeskin/projects/FrequencySliding/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="615" documentId="8_{99D7831B-F734-4922-934A-325255992288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20DB68B4-596B-4B05-B17C-9D5459AA7D6A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99897EDE-C8D8-F546-8217-1480984965AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BDI-II Multi" sheetId="1" r:id="rId1"/>
+    <sheet name="BDI-II_AfterECT" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="112">
   <si>
     <t>SubjectID</t>
   </si>
@@ -443,10 +444,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -737,9 +734,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -822,173 +822,181 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>92</v>
       </c>
       <c r="B2" t="s">
         <v>93</v>
       </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" t="s">
-        <v>50</v>
-      </c>
-      <c r="P2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>50</v>
-      </c>
-      <c r="R2" t="s">
-        <v>50</v>
-      </c>
-      <c r="S2" t="s">
-        <v>50</v>
-      </c>
-      <c r="T2" t="s">
-        <v>50</v>
-      </c>
-      <c r="U2" t="s">
-        <v>50</v>
-      </c>
-      <c r="V2" t="s">
-        <v>50</v>
-      </c>
-      <c r="W2" t="s">
-        <v>50</v>
-      </c>
-      <c r="X2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>50</v>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2" cm="1">
+        <f t="array" ref="X2">SUM(INDEX(C2:W2, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>1</v>
+      </c>
+      <c r="Y2" cm="1">
+        <f t="array" ref="Y2">SUM(INDEX(C2:W2, {4,11,12,13,17,19}))</f>
+        <v>4</v>
+      </c>
+      <c r="Z2" cm="1">
+        <f t="array" ref="Z2">SUM(INDEX(C2:W2, {15,16,18,20,21}))</f>
+        <v>3</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" ref="AA2:AA4" si="0">SUM(C2:W2)</f>
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>94</v>
       </c>
       <c r="B3" t="s">
         <v>95</v>
       </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" t="s">
-        <v>50</v>
-      </c>
-      <c r="N3" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>50</v>
-      </c>
-      <c r="R3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T3" t="s">
-        <v>50</v>
-      </c>
-      <c r="U3" t="s">
-        <v>50</v>
-      </c>
-      <c r="V3" t="s">
-        <v>50</v>
-      </c>
-      <c r="W3" t="s">
-        <v>50</v>
-      </c>
-      <c r="X3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>50</v>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>2</v>
+      </c>
+      <c r="P3">
+        <v>3</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>2</v>
+      </c>
+      <c r="T3">
+        <v>3</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>3</v>
+      </c>
+      <c r="X3" cm="1">
+        <f t="array" ref="X3">SUM(INDEX(C3:W3, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>27</v>
+      </c>
+      <c r="Y3" cm="1">
+        <f t="array" ref="Y3">SUM(INDEX(C3:W3, {4,11,12,13,17,19}))</f>
+        <v>12</v>
+      </c>
+      <c r="Z3" cm="1">
+        <f t="array" ref="Z3">SUM(INDEX(C3:W3, {15,16,18,20,21}))</f>
+        <v>9</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="0"/>
+        <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -1071,343 +1079,359 @@
         <v>6</v>
       </c>
       <c r="AA4">
-        <f t="shared" ref="AA4" si="0">SUM(C4:W4)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>57</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O5" t="s">
-        <v>50</v>
-      </c>
-      <c r="P5" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>50</v>
-      </c>
-      <c r="R5" t="s">
-        <v>50</v>
-      </c>
-      <c r="S5" t="s">
-        <v>50</v>
-      </c>
-      <c r="T5" t="s">
-        <v>50</v>
-      </c>
-      <c r="U5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V5" t="s">
-        <v>50</v>
-      </c>
-      <c r="W5" t="s">
-        <v>50</v>
-      </c>
-      <c r="X5" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>50</v>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>2</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5" cm="1">
+        <f t="array" ref="X5">SUM(INDEX(C5:W5, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>10</v>
+      </c>
+      <c r="Y5" cm="1">
+        <f t="array" ref="Y5">SUM(INDEX(C5:W5, {4,11,12,13,17,19}))</f>
+        <v>10</v>
+      </c>
+      <c r="Z5" cm="1">
+        <f t="array" ref="Z5">SUM(INDEX(C5:W5, {15,16,18,20,21}))</f>
+        <v>5</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" ref="AA5" si="1">SUM(C5:W5)</f>
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>96</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
       </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O6" t="s">
-        <v>50</v>
-      </c>
-      <c r="P6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>50</v>
-      </c>
-      <c r="R6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S6" t="s">
-        <v>50</v>
-      </c>
-      <c r="T6" t="s">
-        <v>50</v>
-      </c>
-      <c r="U6" t="s">
-        <v>50</v>
-      </c>
-      <c r="V6" t="s">
-        <v>50</v>
-      </c>
-      <c r="W6" t="s">
-        <v>50</v>
-      </c>
-      <c r="X6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>50</v>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6">
+        <v>3</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6" cm="1">
+        <f t="array" ref="X6">SUM(INDEX(C6:W6, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>21</v>
+      </c>
+      <c r="Y6" cm="1">
+        <f t="array" ref="Y6">SUM(INDEX(C6:W6, {4,11,12,13,17,19}))</f>
+        <v>10</v>
+      </c>
+      <c r="Z6" cm="1">
+        <f t="array" ref="Z6">SUM(INDEX(C6:W6, {15,16,18,20,21}))</f>
+        <v>11</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" ref="AA6" si="2">SUM(C6:W6)</f>
+        <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>98</v>
       </c>
       <c r="B7" t="s">
         <v>99</v>
       </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" t="s">
-        <v>50</v>
-      </c>
-      <c r="O7" t="s">
-        <v>50</v>
-      </c>
-      <c r="P7" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>50</v>
-      </c>
-      <c r="R7" t="s">
-        <v>50</v>
-      </c>
-      <c r="S7" t="s">
-        <v>50</v>
-      </c>
-      <c r="T7" t="s">
-        <v>50</v>
-      </c>
-      <c r="U7" t="s">
-        <v>50</v>
-      </c>
-      <c r="V7" t="s">
-        <v>50</v>
-      </c>
-      <c r="W7" t="s">
-        <v>50</v>
-      </c>
-      <c r="X7" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>50</v>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
+      </c>
+      <c r="R7">
+        <v>3</v>
+      </c>
+      <c r="S7">
+        <v>2</v>
+      </c>
+      <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7" cm="1">
+        <f t="array" ref="X7">SUM(INDEX(C7:W7, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>23</v>
+      </c>
+      <c r="Y7" cm="1">
+        <f t="array" ref="Y7">SUM(INDEX(C7:W7, {4,11,12,13,17,19}))</f>
+        <v>14</v>
+      </c>
+      <c r="Z7" cm="1">
+        <f t="array" ref="Z7">SUM(INDEX(C7:W7, {15,16,18,20,21}))</f>
+        <v>9</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" ref="AA7" si="3">SUM(C7:W7)</f>
+        <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>100</v>
       </c>
       <c r="B8" t="s">
         <v>101</v>
       </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" t="s">
-        <v>50</v>
-      </c>
-      <c r="O8" t="s">
-        <v>50</v>
-      </c>
-      <c r="P8" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" t="s">
-        <v>50</v>
-      </c>
-      <c r="S8" t="s">
-        <v>50</v>
-      </c>
-      <c r="T8" t="s">
-        <v>50</v>
-      </c>
-      <c r="U8" t="s">
-        <v>50</v>
-      </c>
-      <c r="V8" t="s">
-        <v>50</v>
-      </c>
-      <c r="W8" t="s">
-        <v>50</v>
-      </c>
-      <c r="X8" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>50</v>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>2</v>
+      </c>
+      <c r="O8">
+        <v>2</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+      <c r="R8">
+        <v>2</v>
+      </c>
+      <c r="S8">
+        <v>2</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8" cm="1">
+        <f t="array" ref="X8">SUM(INDEX(C8:W8, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>17</v>
+      </c>
+      <c r="Y8" cm="1">
+        <f t="array" ref="Y8">SUM(INDEX(C8:W8, {4,11,12,13,17,19}))</f>
+        <v>11</v>
+      </c>
+      <c r="Z8" cm="1">
+        <f t="array" ref="Z8">SUM(INDEX(C8:W8, {15,16,18,20,21}))</f>
+        <v>7</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" ref="AA8" si="4">SUM(C8:W8)</f>
+        <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>65</v>
       </c>
@@ -1490,11 +1514,11 @@
         <v>14</v>
       </c>
       <c r="AA9">
-        <f t="shared" ref="AA9" si="1">SUM(C9:W9)</f>
+        <f t="shared" ref="AA9" si="5">SUM(C9:W9)</f>
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -1577,11 +1601,11 @@
         <v>4</v>
       </c>
       <c r="AA10">
-        <f t="shared" ref="AA10:AA11" si="2">SUM(C10:W10)</f>
+        <f t="shared" ref="AA10:AA11" si="6">SUM(C10:W10)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -1664,11 +1688,11 @@
         <v>6</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -1751,11 +1775,11 @@
         <v>13</v>
       </c>
       <c r="AA12">
-        <f t="shared" ref="AA12" si="3">SUM(C12:W12)</f>
+        <f t="shared" ref="AA12" si="7">SUM(C12:W12)</f>
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -1838,19 +1862,98 @@
         <v>6</v>
       </c>
       <c r="AA13">
-        <f t="shared" ref="AA13:AA36" si="4">SUM(C13:W13)</f>
+        <f t="shared" ref="AA13:AA37" si="8">SUM(C13:W13)</f>
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>102</v>
       </c>
       <c r="B14" t="s">
         <v>103</v>
       </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>3</v>
+      </c>
+      <c r="M14">
+        <v>3</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>3</v>
+      </c>
+      <c r="X14" cm="1">
+        <f t="array" ref="X14">SUM(INDEX(C14:W14, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>10</v>
+      </c>
+      <c r="Y14" cm="1">
+        <f t="array" ref="Y14">SUM(INDEX(C14:W14, {4,11,12,13,17,19}))</f>
+        <v>8</v>
+      </c>
+      <c r="Z14" cm="1">
+        <f t="array" ref="Z14">SUM(INDEX(C14:W14, {15,16,18,20,21}))</f>
+        <v>4</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="8"/>
+        <v>22</v>
+      </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -1933,11 +2036,11 @@
         <v>4</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -2020,94 +2123,98 @@
         <v>2</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17" t="s">
         <v>105</v>
       </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" t="s">
-        <v>50</v>
-      </c>
-      <c r="K17" t="s">
-        <v>50</v>
-      </c>
-      <c r="L17" t="s">
-        <v>50</v>
-      </c>
-      <c r="M17" t="s">
-        <v>50</v>
-      </c>
-      <c r="N17" t="s">
-        <v>50</v>
-      </c>
-      <c r="O17" t="s">
-        <v>50</v>
-      </c>
-      <c r="P17" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>50</v>
-      </c>
-      <c r="R17" t="s">
-        <v>50</v>
-      </c>
-      <c r="S17" t="s">
-        <v>50</v>
-      </c>
-      <c r="T17" t="s">
-        <v>50</v>
-      </c>
-      <c r="U17" t="s">
-        <v>50</v>
-      </c>
-      <c r="V17" t="s">
-        <v>50</v>
-      </c>
-      <c r="W17" t="s">
-        <v>50</v>
-      </c>
-      <c r="X17" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>50</v>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>2</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>3</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17" cm="1">
+        <f t="array" ref="X17">SUM(INDEX(C17:W17, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>13</v>
+      </c>
+      <c r="Y17" cm="1">
+        <f t="array" ref="Y17">SUM(INDEX(C17:W17, {4,11,12,13,17,19}))</f>
+        <v>6</v>
+      </c>
+      <c r="Z17" cm="1">
+        <f t="array" ref="Z17">SUM(INDEX(C17:W17, {15,16,18,20,21}))</f>
+        <v>6</v>
+      </c>
+      <c r="AA17">
+        <f t="shared" ref="AA17" si="9">SUM(C17:W17)</f>
+        <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -2190,11 +2297,11 @@
         <v>11</v>
       </c>
       <c r="AA18">
-        <f t="shared" ref="AA18" si="5">SUM(C18:W18)</f>
+        <f t="shared" ref="AA18" si="10">SUM(C18:W18)</f>
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>106</v>
       </c>
@@ -2277,177 +2384,185 @@
         <v>4</v>
       </c>
       <c r="AA19">
-        <f t="shared" ref="AA19" si="6">SUM(C19:W19)</f>
+        <f t="shared" ref="AA19" si="11">SUM(C19:W19)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>108</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
-      <c r="C20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G20" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" t="s">
-        <v>50</v>
-      </c>
-      <c r="I20" t="s">
-        <v>50</v>
-      </c>
-      <c r="J20" t="s">
-        <v>50</v>
-      </c>
-      <c r="K20" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" t="s">
-        <v>50</v>
-      </c>
-      <c r="M20" t="s">
-        <v>50</v>
-      </c>
-      <c r="N20" t="s">
-        <v>50</v>
-      </c>
-      <c r="O20" t="s">
-        <v>50</v>
-      </c>
-      <c r="P20" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>50</v>
-      </c>
-      <c r="R20" t="s">
-        <v>50</v>
-      </c>
-      <c r="S20" t="s">
-        <v>50</v>
-      </c>
-      <c r="T20" t="s">
-        <v>50</v>
-      </c>
-      <c r="U20" t="s">
-        <v>50</v>
-      </c>
-      <c r="V20" t="s">
-        <v>50</v>
-      </c>
-      <c r="W20" t="s">
-        <v>50</v>
-      </c>
-      <c r="X20" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>50</v>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>2</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>2</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>2</v>
+      </c>
+      <c r="X20" cm="1">
+        <f t="array" ref="X20">SUM(INDEX(C20:W20, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>8</v>
+      </c>
+      <c r="Y20" cm="1">
+        <f t="array" ref="Y20">SUM(INDEX(C20:W20, {4,11,12,13,17,19}))</f>
+        <v>7</v>
+      </c>
+      <c r="Z20" cm="1">
+        <f t="array" ref="Z20">SUM(INDEX(C20:W20, {15,16,18,20,21}))</f>
+        <v>3</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" ref="AA20" si="12">SUM(C20:W20)</f>
+        <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>110</v>
       </c>
       <c r="B21" t="s">
         <v>111</v>
       </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G21" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" t="s">
-        <v>50</v>
-      </c>
-      <c r="K21" t="s">
-        <v>50</v>
-      </c>
-      <c r="L21" t="s">
-        <v>50</v>
-      </c>
-      <c r="M21" t="s">
-        <v>50</v>
-      </c>
-      <c r="N21" t="s">
-        <v>50</v>
-      </c>
-      <c r="O21" t="s">
-        <v>50</v>
-      </c>
-      <c r="P21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>50</v>
-      </c>
-      <c r="R21" t="s">
-        <v>50</v>
-      </c>
-      <c r="S21" t="s">
-        <v>50</v>
-      </c>
-      <c r="T21" t="s">
-        <v>50</v>
-      </c>
-      <c r="U21" t="s">
-        <v>50</v>
-      </c>
-      <c r="V21" t="s">
-        <v>50</v>
-      </c>
-      <c r="W21" t="s">
-        <v>50</v>
-      </c>
-      <c r="X21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>50</v>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>3</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21" cm="1">
+        <f t="array" ref="X21">SUM(INDEX(C21:W21, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y21" cm="1">
+        <f t="array" ref="Y21">SUM(INDEX(C21:W21, {4,11,12,13,17,19}))</f>
+        <v>4</v>
+      </c>
+      <c r="Z21" cm="1">
+        <f t="array" ref="Z21">SUM(INDEX(C21:W21, {15,16,18,20,21}))</f>
+        <v>3</v>
+      </c>
+      <c r="AA21">
+        <f t="shared" ref="AA21" si="13">SUM(C21:W21)</f>
+        <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -2530,11 +2645,11 @@
         <v>3</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -2617,11 +2732,11 @@
         <v>6</v>
       </c>
       <c r="AA23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -2704,11 +2819,11 @@
         <v>8</v>
       </c>
       <c r="AA24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -2791,11 +2906,11 @@
         <v>10</v>
       </c>
       <c r="AA25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -2878,94 +2993,98 @@
         <v>6</v>
       </c>
       <c r="AA26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>81</v>
       </c>
       <c r="B27" t="s">
         <v>82</v>
       </c>
-      <c r="C27" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" t="s">
-        <v>50</v>
-      </c>
-      <c r="E27" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G27" t="s">
-        <v>50</v>
-      </c>
-      <c r="H27" t="s">
-        <v>50</v>
-      </c>
-      <c r="I27" t="s">
-        <v>50</v>
-      </c>
-      <c r="J27" t="s">
-        <v>50</v>
-      </c>
-      <c r="K27" t="s">
-        <v>50</v>
-      </c>
-      <c r="L27" t="s">
-        <v>50</v>
-      </c>
-      <c r="M27" t="s">
-        <v>50</v>
-      </c>
-      <c r="N27" t="s">
-        <v>50</v>
-      </c>
-      <c r="O27" t="s">
-        <v>50</v>
-      </c>
-      <c r="P27" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>50</v>
-      </c>
-      <c r="R27" t="s">
-        <v>50</v>
-      </c>
-      <c r="S27" t="s">
-        <v>50</v>
-      </c>
-      <c r="T27" t="s">
-        <v>50</v>
-      </c>
-      <c r="U27" t="s">
-        <v>50</v>
-      </c>
-      <c r="V27" t="s">
-        <v>50</v>
-      </c>
-      <c r="W27" t="s">
-        <v>50</v>
-      </c>
-      <c r="X27" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>50</v>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>3</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27">
+        <v>3</v>
+      </c>
+      <c r="M27">
+        <v>3</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27">
+        <v>3</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>2</v>
+      </c>
+      <c r="S27">
+        <v>3</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27" cm="1">
+        <f t="array" ref="X27">SUM(INDEX(C27:W27, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>27</v>
+      </c>
+      <c r="Y27" cm="1">
+        <f t="array" ref="Y27">SUM(INDEX(C27:W27, {4,11,12,13,17,19}))</f>
+        <v>15</v>
+      </c>
+      <c r="Z27" cm="1">
+        <f t="array" ref="Z27">SUM(INDEX(C27:W27, {15,16,18,20,21}))</f>
+        <v>5</v>
+      </c>
+      <c r="AA27">
+        <f t="shared" ref="AA27" si="14">SUM(C27:W27)</f>
+        <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -3048,11 +3167,11 @@
         <v>7</v>
       </c>
       <c r="AA28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -3135,11 +3254,11 @@
         <v>3</v>
       </c>
       <c r="AA29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -3222,11 +3341,11 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -3309,11 +3428,11 @@
         <v>12</v>
       </c>
       <c r="AA31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -3400,7 +3519,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>83</v>
       </c>
@@ -3487,90 +3606,94 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>85</v>
       </c>
       <c r="B34" t="s">
         <v>86</v>
       </c>
-      <c r="C34" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" t="s">
-        <v>50</v>
-      </c>
-      <c r="F34" t="s">
-        <v>50</v>
-      </c>
-      <c r="G34" t="s">
-        <v>50</v>
-      </c>
-      <c r="H34" t="s">
-        <v>50</v>
-      </c>
-      <c r="I34" t="s">
-        <v>50</v>
-      </c>
-      <c r="J34" t="s">
-        <v>50</v>
-      </c>
-      <c r="K34" t="s">
-        <v>50</v>
-      </c>
-      <c r="L34" t="s">
-        <v>50</v>
-      </c>
-      <c r="M34" t="s">
-        <v>50</v>
-      </c>
-      <c r="N34" t="s">
-        <v>50</v>
-      </c>
-      <c r="O34" t="s">
-        <v>50</v>
-      </c>
-      <c r="P34" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>50</v>
-      </c>
-      <c r="R34" t="s">
-        <v>50</v>
-      </c>
-      <c r="S34" t="s">
-        <v>50</v>
-      </c>
-      <c r="T34" t="s">
-        <v>50</v>
-      </c>
-      <c r="U34" t="s">
-        <v>50</v>
-      </c>
-      <c r="V34" t="s">
-        <v>50</v>
-      </c>
-      <c r="W34" t="s">
-        <v>50</v>
-      </c>
-      <c r="X34" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>50</v>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34">
+        <v>3</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>2</v>
+      </c>
+      <c r="O34">
+        <v>3</v>
+      </c>
+      <c r="P34">
+        <v>1</v>
+      </c>
+      <c r="Q34">
+        <v>2</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>2</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>11</v>
+      </c>
+      <c r="X34" cm="1">
+        <f t="array" ref="X34">SUM(INDEX(C34:W34, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>20</v>
+      </c>
+      <c r="Y34" cm="1">
+        <f t="array" ref="Y34">SUM(INDEX(C34:W34, {4,11,12,13,17,19}))</f>
+        <v>9</v>
+      </c>
+      <c r="Z34" cm="1">
+        <f t="array" ref="Z34">SUM(INDEX(C34:W34, {15,16,18,20,21}))</f>
+        <v>13</v>
+      </c>
+      <c r="AA34">
+        <f>SUM(C34:W34)</f>
+        <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -3653,11 +3776,11 @@
         <v>9</v>
       </c>
       <c r="AA35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -3740,19 +3863,98 @@
         <v>6</v>
       </c>
       <c r="AA36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>77</v>
       </c>
       <c r="B37" t="s">
         <v>78</v>
       </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37">
+        <v>3</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="Q37">
+        <v>3</v>
+      </c>
+      <c r="R37">
+        <v>3</v>
+      </c>
+      <c r="S37">
+        <v>2</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>1</v>
+      </c>
+      <c r="V37">
+        <v>1</v>
+      </c>
+      <c r="W37">
+        <v>2</v>
+      </c>
+      <c r="X37" cm="1">
+        <f t="array" ref="X37">SUM(INDEX(C37:W37, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>17</v>
+      </c>
+      <c r="Y37" cm="1">
+        <f t="array" ref="Y37">SUM(INDEX(C37:W37, {4,11,12,13,17,19}))</f>
+        <v>11</v>
+      </c>
+      <c r="Z37" cm="1">
+        <f t="array" ref="Z37">SUM(INDEX(C37:W37, {15,16,18,20,21}))</f>
+        <v>9</v>
+      </c>
+      <c r="AA37">
+        <f t="shared" si="8"/>
+        <v>37</v>
+      </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -3839,173 +4041,181 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>87</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
       </c>
-      <c r="C39" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" t="s">
-        <v>50</v>
-      </c>
-      <c r="F39" t="s">
-        <v>50</v>
-      </c>
-      <c r="G39" t="s">
-        <v>50</v>
-      </c>
-      <c r="H39" t="s">
-        <v>50</v>
-      </c>
-      <c r="I39" t="s">
-        <v>50</v>
-      </c>
-      <c r="J39" t="s">
-        <v>50</v>
-      </c>
-      <c r="K39" t="s">
-        <v>50</v>
-      </c>
-      <c r="L39" t="s">
-        <v>50</v>
-      </c>
-      <c r="M39" t="s">
-        <v>50</v>
-      </c>
-      <c r="N39" t="s">
-        <v>50</v>
-      </c>
-      <c r="O39" t="s">
-        <v>50</v>
-      </c>
-      <c r="P39" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>50</v>
-      </c>
-      <c r="R39" t="s">
-        <v>50</v>
-      </c>
-      <c r="S39" t="s">
-        <v>50</v>
-      </c>
-      <c r="T39" t="s">
-        <v>50</v>
-      </c>
-      <c r="U39" t="s">
-        <v>50</v>
-      </c>
-      <c r="V39" t="s">
-        <v>50</v>
-      </c>
-      <c r="W39" t="s">
-        <v>50</v>
-      </c>
-      <c r="X39" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA39" t="s">
-        <v>50</v>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>2</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="Q39">
+        <v>3</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>3</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>1</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39" cm="1">
+        <f t="array" ref="X39">SUM(INDEX(C39:W39, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>11</v>
+      </c>
+      <c r="Y39" cm="1">
+        <f t="array" ref="Y39">SUM(INDEX(C39:W39, {4,11,12,13,17,19}))</f>
+        <v>8</v>
+      </c>
+      <c r="Z39" cm="1">
+        <f t="array" ref="Z39">SUM(INDEX(C39:W39, {15,16,18,20,21}))</f>
+        <v>4</v>
+      </c>
+      <c r="AA39">
+        <f>SUM(C39:W39)</f>
+        <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>88</v>
       </c>
       <c r="B40" t="s">
         <v>89</v>
       </c>
-      <c r="C40" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" t="s">
-        <v>50</v>
-      </c>
-      <c r="F40" t="s">
-        <v>50</v>
-      </c>
-      <c r="G40" t="s">
-        <v>50</v>
-      </c>
-      <c r="H40" t="s">
-        <v>50</v>
-      </c>
-      <c r="I40" t="s">
-        <v>50</v>
-      </c>
-      <c r="J40" t="s">
-        <v>50</v>
-      </c>
-      <c r="K40" t="s">
-        <v>50</v>
-      </c>
-      <c r="L40" t="s">
-        <v>50</v>
-      </c>
-      <c r="M40" t="s">
-        <v>50</v>
-      </c>
-      <c r="N40" t="s">
-        <v>50</v>
-      </c>
-      <c r="O40" t="s">
-        <v>50</v>
-      </c>
-      <c r="P40" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>50</v>
-      </c>
-      <c r="R40" t="s">
-        <v>50</v>
-      </c>
-      <c r="S40" t="s">
-        <v>50</v>
-      </c>
-      <c r="T40" t="s">
-        <v>50</v>
-      </c>
-      <c r="U40" t="s">
-        <v>50</v>
-      </c>
-      <c r="V40" t="s">
-        <v>50</v>
-      </c>
-      <c r="W40" t="s">
-        <v>50</v>
-      </c>
-      <c r="X40" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>50</v>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>3</v>
+      </c>
+      <c r="K40">
+        <v>3</v>
+      </c>
+      <c r="L40">
+        <v>3</v>
+      </c>
+      <c r="M40">
+        <v>3</v>
+      </c>
+      <c r="N40">
+        <v>3</v>
+      </c>
+      <c r="O40">
+        <v>2</v>
+      </c>
+      <c r="P40">
+        <v>3</v>
+      </c>
+      <c r="Q40">
+        <v>3</v>
+      </c>
+      <c r="R40">
+        <v>3</v>
+      </c>
+      <c r="S40">
+        <v>3</v>
+      </c>
+      <c r="T40">
+        <v>2</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40">
+        <v>1</v>
+      </c>
+      <c r="W40">
+        <v>2</v>
+      </c>
+      <c r="X40" cm="1">
+        <f t="array" ref="X40">SUM(INDEX(C40:W40, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>27</v>
+      </c>
+      <c r="Y40" cm="1">
+        <f t="array" ref="Y40">SUM(INDEX(C40:W40, {4,11,12,13,17,19}))</f>
+        <v>15</v>
+      </c>
+      <c r="Z40" cm="1">
+        <f t="array" ref="Z40">SUM(INDEX(C40:W40, {15,16,18,20,21}))</f>
+        <v>11</v>
+      </c>
+      <c r="AA40">
+        <f t="shared" ref="AA39:AA40" si="15">SUM(C40:W40)</f>
+        <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -4088,7 +4298,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -4175,7 +4385,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -4260,6 +4470,1143 @@
       <c r="AA43">
         <f>SUM(C43:W43)</f>
         <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C53C76-FF94-D249-AA9A-6F4764C599CE}">
+  <dimension ref="A1:AA13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>2</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2" cm="1">
+        <f t="array" ref="X2">SUM(INDEX(C2:W2, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>0</v>
+      </c>
+      <c r="Y2" cm="1">
+        <f t="array" ref="Y2">SUM(INDEX(C2:W2, {4,11,12,13,17,19}))</f>
+        <v>2</v>
+      </c>
+      <c r="Z2" cm="1">
+        <f t="array" ref="Z2">SUM(INDEX(C2:W2, {15,16,18,20,21}))</f>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" ref="AA2:AA13" si="0">SUM(C2:W2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>3</v>
+      </c>
+      <c r="X3" cm="1">
+        <f t="array" ref="X3">SUM(INDEX(C3:W3, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>10</v>
+      </c>
+      <c r="Y3" cm="1">
+        <f t="array" ref="Y3">SUM(INDEX(C3:W3, {4,11,12,13,17,19}))</f>
+        <v>9</v>
+      </c>
+      <c r="Z3" cm="1">
+        <f t="array" ref="Z3">SUM(INDEX(C3:W3, {15,16,18,20,21}))</f>
+        <v>5</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4" cm="1">
+        <f t="array" ref="X4">SUM(INDEX(C4:W4, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>2</v>
+      </c>
+      <c r="Y4" cm="1">
+        <f t="array" ref="Y4">SUM(INDEX(C4:W4, {4,11,12,13,17,19}))</f>
+        <v>1</v>
+      </c>
+      <c r="Z4" cm="1">
+        <f t="array" ref="Z4">SUM(INDEX(C4:W4, {15,16,18,20,21}))</f>
+        <v>4</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5" cm="1">
+        <f t="array" ref="X5">SUM(INDEX(C5:W5, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>13</v>
+      </c>
+      <c r="Y5" cm="1">
+        <f t="array" ref="Y5">SUM(INDEX(C5:W5, {4,11,12,13,17,19}))</f>
+        <v>4</v>
+      </c>
+      <c r="Z5" cm="1">
+        <f t="array" ref="Z5">SUM(INDEX(C5:W5, {15,16,18,20,21}))</f>
+        <v>6</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6" cm="1">
+        <f t="array" ref="X6">SUM(INDEX(C6:W6, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>9</v>
+      </c>
+      <c r="Y6" cm="1">
+        <f t="array" ref="Y6">SUM(INDEX(C6:W6, {4,11,12,13,17,19}))</f>
+        <v>5</v>
+      </c>
+      <c r="Z6" cm="1">
+        <f t="array" ref="Z6">SUM(INDEX(C6:W6, {15,16,18,20,21}))</f>
+        <v>3</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7" cm="1">
+        <f t="array" ref="X7">SUM(INDEX(C7:W7, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>8</v>
+      </c>
+      <c r="Y7" cm="1">
+        <f t="array" ref="Y7">SUM(INDEX(C7:W7, {4,11,12,13,17,19}))</f>
+        <v>3</v>
+      </c>
+      <c r="Z7" cm="1">
+        <f t="array" ref="Z7">SUM(INDEX(C7:W7, {15,16,18,20,21}))</f>
+        <v>2</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8" cm="1">
+        <f t="array" ref="X8">SUM(INDEX(C8:W8, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>10</v>
+      </c>
+      <c r="Y8" cm="1">
+        <f t="array" ref="Y8">SUM(INDEX(C8:W8, {4,11,12,13,17,19}))</f>
+        <v>8</v>
+      </c>
+      <c r="Z8" cm="1">
+        <f t="array" ref="Z8">SUM(INDEX(C8:W8, {15,16,18,20,21}))</f>
+        <v>4</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9" cm="1">
+        <f t="array" ref="X9">SUM(INDEX(C9:W9, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>1</v>
+      </c>
+      <c r="Y9" cm="1">
+        <f t="array" ref="Y9">SUM(INDEX(C9:W9, {4,11,12,13,17,19}))</f>
+        <v>3</v>
+      </c>
+      <c r="Z9" cm="1">
+        <f t="array" ref="Z9">SUM(INDEX(C9:W9, {15,16,18,20,21}))</f>
+        <v>2</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10" cm="1">
+        <f t="array" ref="X10">SUM(INDEX(C10:W10, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y10" cm="1">
+        <f t="array" ref="Y10">SUM(INDEX(C10:W10, {4,11,12,13,17,19}))</f>
+        <v>0</v>
+      </c>
+      <c r="Z10" cm="1">
+        <f t="array" ref="Z10">SUM(INDEX(C10:W10, {15,16,18,20,21}))</f>
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11" cm="1">
+        <f t="array" ref="X11">SUM(INDEX(C11:W11, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>1</v>
+      </c>
+      <c r="Y11" cm="1">
+        <f t="array" ref="Y11">SUM(INDEX(C11:W11, {4,11,12,13,17,19}))</f>
+        <v>1</v>
+      </c>
+      <c r="Z11" cm="1">
+        <f t="array" ref="Z11">SUM(INDEX(C11:W11, {15,16,18,20,21}))</f>
+        <v>2</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>2</v>
+      </c>
+      <c r="W12">
+        <v>2</v>
+      </c>
+      <c r="X12" cm="1">
+        <f t="array" ref="X12">SUM(INDEX(C12:W12, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>2</v>
+      </c>
+      <c r="Y12" cm="1">
+        <f t="array" ref="Y12">SUM(INDEX(C12:W12, {4,11,12,13,17,19}))</f>
+        <v>5</v>
+      </c>
+      <c r="Z12" cm="1">
+        <f t="array" ref="Z12">SUM(INDEX(C12:W12, {15,16,18,20,21}))</f>
+        <v>6</v>
+      </c>
+      <c r="AA12">
+        <f>SUM(C12:W12)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>3</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>2</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>3</v>
+      </c>
+      <c r="X13" cm="1">
+        <f t="array" ref="X13">SUM(INDEX(C13:W13, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>20</v>
+      </c>
+      <c r="Y13" cm="1">
+        <f t="array" ref="Y13">SUM(INDEX(C13:W13, {4,11,12,13,17,19}))</f>
+        <v>9</v>
+      </c>
+      <c r="Z13" cm="1">
+        <f t="array" ref="Z13">SUM(INDEX(C13:W13, {15,16,18,20,21}))</f>
+        <v>6</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
+++ b/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaankeskin/projects/FrequencySliding/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99897EDE-C8D8-F546-8217-1480984965AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD392507-353F-844D-8E7A-EF6D0A11906C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="660" windowWidth="18960" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BDI-II Multi" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="114">
   <si>
     <t>SubjectID</t>
   </si>
@@ -392,6 +392,12 @@
   </si>
   <si>
     <t>sub-20</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Sex</t>
   </si>
 </sst>
 </file>
@@ -733,13 +739,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -821,8 +827,14 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>113</v>
+      </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -908,8 +920,14 @@
         <f t="shared" ref="AA2:AA4" si="0">SUM(C2:W2)</f>
         <v>8</v>
       </c>
+      <c r="AB2">
+        <v>56</v>
+      </c>
+      <c r="AC2">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -995,8 +1013,14 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
+      <c r="AB3">
+        <v>36</v>
+      </c>
+      <c r="AC3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -1082,8 +1106,14 @@
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
+      <c r="AB4">
+        <v>39</v>
+      </c>
+      <c r="AC4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -1169,8 +1199,14 @@
         <f t="shared" ref="AA5" si="1">SUM(C5:W5)</f>
         <v>25</v>
       </c>
+      <c r="AB5">
+        <v>49</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -1256,8 +1292,14 @@
         <f t="shared" ref="AA6" si="2">SUM(C6:W6)</f>
         <v>42</v>
       </c>
+      <c r="AB6">
+        <v>27</v>
+      </c>
+      <c r="AC6">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -1343,8 +1385,14 @@
         <f t="shared" ref="AA7" si="3">SUM(C7:W7)</f>
         <v>46</v>
       </c>
+      <c r="AB7">
+        <v>32</v>
+      </c>
+      <c r="AC7">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>100</v>
       </c>
@@ -1430,8 +1478,14 @@
         <f t="shared" ref="AA8" si="4">SUM(C8:W8)</f>
         <v>35</v>
       </c>
+      <c r="AB8">
+        <v>51</v>
+      </c>
+      <c r="AC8">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>65</v>
       </c>
@@ -1517,8 +1571,14 @@
         <f t="shared" ref="AA9" si="5">SUM(C9:W9)</f>
         <v>54</v>
       </c>
+      <c r="AB9">
+        <v>20</v>
+      </c>
+      <c r="AC9">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -1604,8 +1664,14 @@
         <f t="shared" ref="AA10:AA11" si="6">SUM(C10:W10)</f>
         <v>24</v>
       </c>
+      <c r="AB10">
+        <v>54</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -1691,8 +1757,14 @@
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
+      <c r="AB11">
+        <v>26</v>
+      </c>
+      <c r="AC11">
+        <v>2</v>
+      </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -1778,8 +1850,14 @@
         <f t="shared" ref="AA12" si="7">SUM(C12:W12)</f>
         <v>44</v>
       </c>
+      <c r="AB12">
+        <v>54</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -1865,8 +1943,14 @@
         <f t="shared" ref="AA13:AA37" si="8">SUM(C13:W13)</f>
         <v>38</v>
       </c>
+      <c r="AB13">
+        <v>40</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>102</v>
       </c>
@@ -1952,8 +2036,14 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
+      <c r="AB14">
+        <v>52</v>
+      </c>
+      <c r="AC14">
+        <v>2</v>
+      </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -2039,8 +2129,14 @@
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
+      <c r="AB15">
+        <v>34</v>
+      </c>
+      <c r="AC15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -2126,8 +2222,14 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
+      <c r="AB16">
+        <v>23</v>
+      </c>
+      <c r="AC16">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>104</v>
       </c>
@@ -2213,8 +2315,14 @@
         <f t="shared" ref="AA17" si="9">SUM(C17:W17)</f>
         <v>25</v>
       </c>
+      <c r="AB17">
+        <v>31</v>
+      </c>
+      <c r="AC17">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -2300,8 +2408,14 @@
         <f t="shared" ref="AA18" si="10">SUM(C18:W18)</f>
         <v>52</v>
       </c>
+      <c r="AB18">
+        <v>19</v>
+      </c>
+      <c r="AC18">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>106</v>
       </c>
@@ -2387,8 +2501,14 @@
         <f t="shared" ref="AA19" si="11">SUM(C19:W19)</f>
         <v>25</v>
       </c>
+      <c r="AB19">
+        <v>30</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>108</v>
       </c>
@@ -2474,8 +2594,14 @@
         <f t="shared" ref="AA20" si="12">SUM(C20:W20)</f>
         <v>18</v>
       </c>
+      <c r="AB20">
+        <v>30</v>
+      </c>
+      <c r="AC20">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -2561,8 +2687,14 @@
         <f t="shared" ref="AA21" si="13">SUM(C21:W21)</f>
         <v>13</v>
       </c>
+      <c r="AB21">
+        <v>47</v>
+      </c>
+      <c r="AC21">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -2648,8 +2780,14 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
+      <c r="AB22">
+        <v>39</v>
+      </c>
+      <c r="AC22">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -2735,8 +2873,14 @@
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
+      <c r="AB23">
+        <v>55</v>
+      </c>
+      <c r="AC23">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -2822,8 +2966,14 @@
         <f t="shared" si="8"/>
         <v>32</v>
       </c>
+      <c r="AB24">
+        <v>42</v>
+      </c>
+      <c r="AC24">
+        <v>2</v>
+      </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -2910,7 +3060,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -2997,7 +3147,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>81</v>
       </c>
@@ -3084,7 +3234,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -3171,7 +3321,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -3258,7 +3408,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -3345,7 +3495,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -3432,7 +3582,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -4211,7 +4361,7 @@
         <v>11</v>
       </c>
       <c r="AA40">
-        <f t="shared" ref="AA39:AA40" si="15">SUM(C40:W40)</f>
+        <f t="shared" ref="AA40" si="15">SUM(C40:W40)</f>
         <v>53</v>
       </c>
     </row>

--- a/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
+++ b/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaankeskin/projects/FrequencySliding/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9860f92a834cae8/Belgeler/GitHub/FrequencySliding/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD392507-353F-844D-8E7A-EF6D0A11906C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{CD392507-353F-844D-8E7A-EF6D0A11906C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A379D40-2F32-42DE-96F5-B2A9B8BEC40E}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="660" windowWidth="18960" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BDI-II Multi" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="116">
   <si>
     <t>SubjectID</t>
   </si>
@@ -398,6 +398,12 @@
   </si>
   <si>
     <t>Sex</t>
+  </si>
+  <si>
+    <t>DoI</t>
+  </si>
+  <si>
+    <t>Education</t>
   </si>
 </sst>
 </file>
@@ -739,13 +745,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AE43"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -833,8 +839,14 @@
       <c r="AC1" t="s">
         <v>113</v>
       </c>
+      <c r="AD1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>115</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -927,7 +939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -1020,7 +1032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -1112,8 +1124,14 @@
       <c r="AC4">
         <v>2</v>
       </c>
+      <c r="AD4">
+        <v>12</v>
+      </c>
+      <c r="AE4">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -1205,8 +1223,14 @@
       <c r="AC5">
         <v>1</v>
       </c>
+      <c r="AD5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE5">
+        <v>12</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -1299,7 +1323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -1392,7 +1416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>100</v>
       </c>
@@ -1485,7 +1509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>65</v>
       </c>
@@ -1577,8 +1601,14 @@
       <c r="AC9">
         <v>2</v>
       </c>
+      <c r="AD9">
+        <v>6</v>
+      </c>
+      <c r="AE9">
+        <v>12</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -1670,8 +1700,14 @@
       <c r="AC10">
         <v>1</v>
       </c>
+      <c r="AD10">
+        <v>29</v>
+      </c>
+      <c r="AE10">
+        <v>12</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -1763,8 +1799,14 @@
       <c r="AC11">
         <v>2</v>
       </c>
+      <c r="AD11">
+        <v>12</v>
+      </c>
+      <c r="AE11">
+        <v>12</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -1856,8 +1898,14 @@
       <c r="AC12">
         <v>1</v>
       </c>
+      <c r="AD12">
+        <v>30</v>
+      </c>
+      <c r="AE12">
+        <v>14</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -1949,8 +1997,14 @@
       <c r="AC13">
         <v>1</v>
       </c>
+      <c r="AD13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE13">
+        <v>12</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>102</v>
       </c>
@@ -2043,7 +2097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -2135,8 +2189,14 @@
       <c r="AC15">
         <v>2</v>
       </c>
+      <c r="AD15">
+        <v>13</v>
+      </c>
+      <c r="AE15">
+        <v>16</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -2228,8 +2288,14 @@
       <c r="AC16">
         <v>2</v>
       </c>
+      <c r="AD16">
+        <v>1</v>
+      </c>
+      <c r="AE16">
+        <v>12</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>104</v>
       </c>
@@ -2322,7 +2388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -2414,8 +2480,14 @@
       <c r="AC18">
         <v>2</v>
       </c>
+      <c r="AD18">
+        <v>5</v>
+      </c>
+      <c r="AE18">
+        <v>12</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>106</v>
       </c>
@@ -2507,8 +2579,14 @@
       <c r="AC19">
         <v>1</v>
       </c>
+      <c r="AD19">
+        <v>4</v>
+      </c>
+      <c r="AE19">
+        <v>8</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>108</v>
       </c>
@@ -2601,7 +2679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -2694,7 +2772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -2786,8 +2864,14 @@
       <c r="AC22">
         <v>2</v>
       </c>
+      <c r="AD22">
+        <v>18</v>
+      </c>
+      <c r="AE22">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -2879,8 +2963,14 @@
       <c r="AC23">
         <v>2</v>
       </c>
+      <c r="AD23">
+        <v>8</v>
+      </c>
+      <c r="AE23">
+        <v>16</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -2972,8 +3062,14 @@
       <c r="AC24">
         <v>2</v>
       </c>
+      <c r="AD24">
+        <v>22</v>
+      </c>
+      <c r="AE24">
+        <v>8</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -3059,8 +3155,20 @@
         <f t="shared" si="8"/>
         <v>33</v>
       </c>
+      <c r="AB25">
+        <v>24</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AD25">
+        <v>4</v>
+      </c>
+      <c r="AE25">
+        <v>12</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -3146,8 +3254,20 @@
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
+      <c r="AB26">
+        <v>21</v>
+      </c>
+      <c r="AC26">
+        <v>1</v>
+      </c>
+      <c r="AD26">
+        <v>4</v>
+      </c>
+      <c r="AE26">
+        <v>12</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>81</v>
       </c>
@@ -3234,7 +3354,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -3320,8 +3440,20 @@
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
+      <c r="AB28">
+        <v>43</v>
+      </c>
+      <c r="AC28">
+        <v>2</v>
+      </c>
+      <c r="AD28">
+        <v>5</v>
+      </c>
+      <c r="AE28">
+        <v>11</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -3407,8 +3539,20 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
+      <c r="AB29">
+        <v>50</v>
+      </c>
+      <c r="AC29">
+        <v>2</v>
+      </c>
+      <c r="AD29">
+        <v>20</v>
+      </c>
+      <c r="AE29">
+        <v>14</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -3494,8 +3638,20 @@
         <f t="shared" si="8"/>
         <v>32</v>
       </c>
+      <c r="AB30">
+        <v>33</v>
+      </c>
+      <c r="AC30">
+        <v>2</v>
+      </c>
+      <c r="AD30">
+        <v>9</v>
+      </c>
+      <c r="AE30">
+        <v>8</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -3581,8 +3737,20 @@
         <f t="shared" si="8"/>
         <v>35</v>
       </c>
+      <c r="AB31">
+        <v>42</v>
+      </c>
+      <c r="AC31">
+        <v>2</v>
+      </c>
+      <c r="AD31">
+        <v>14</v>
+      </c>
+      <c r="AE31">
+        <v>12</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -3668,8 +3836,20 @@
         <f>SUM(C32:W32)</f>
         <v>32</v>
       </c>
+      <c r="AB32">
+        <v>46</v>
+      </c>
+      <c r="AC32">
+        <v>2</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE32">
+        <v>8</v>
+      </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>83</v>
       </c>
@@ -3755,8 +3935,20 @@
         <f>SUM(C33:W33)</f>
         <v>41</v>
       </c>
+      <c r="AB33">
+        <v>43</v>
+      </c>
+      <c r="AC33">
+        <v>2</v>
+      </c>
+      <c r="AD33">
+        <v>10</v>
+      </c>
+      <c r="AE33">
+        <v>8</v>
+      </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -3843,7 +4035,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -3929,8 +4121,20 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
+      <c r="AB35">
+        <v>36</v>
+      </c>
+      <c r="AC35">
+        <v>2</v>
+      </c>
+      <c r="AD35">
+        <v>14</v>
+      </c>
+      <c r="AE35">
+        <v>12</v>
+      </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -4016,8 +4220,20 @@
         <f t="shared" si="8"/>
         <v>32</v>
       </c>
+      <c r="AB36">
+        <v>46</v>
+      </c>
+      <c r="AC36">
+        <v>1</v>
+      </c>
+      <c r="AD36">
+        <v>3</v>
+      </c>
+      <c r="AE36">
+        <v>12</v>
+      </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -4104,7 +4320,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -4190,8 +4406,20 @@
         <f>SUM(C38:W38)</f>
         <v>22</v>
       </c>
+      <c r="AB38">
+        <v>39</v>
+      </c>
+      <c r="AC38">
+        <v>1</v>
+      </c>
+      <c r="AD38">
+        <v>1</v>
+      </c>
+      <c r="AE38">
+        <v>18</v>
+      </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -4278,7 +4506,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -4365,7 +4593,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -4447,8 +4675,20 @@
       <c r="AA41" t="s">
         <v>50</v>
       </c>
+      <c r="AB41">
+        <v>46</v>
+      </c>
+      <c r="AC41">
+        <v>2</v>
+      </c>
+      <c r="AD41">
+        <v>15</v>
+      </c>
+      <c r="AE41">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -4534,8 +4774,20 @@
         <f>SUM(C42:W42)</f>
         <v>46</v>
       </c>
+      <c r="AB42">
+        <v>45</v>
+      </c>
+      <c r="AC42">
+        <v>1</v>
+      </c>
+      <c r="AD42">
+        <v>27</v>
+      </c>
+      <c r="AE42">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -4620,6 +4872,18 @@
       <c r="AA43">
         <f>SUM(C43:W43)</f>
         <v>10</v>
+      </c>
+      <c r="AB43">
+        <v>43</v>
+      </c>
+      <c r="AC43">
+        <v>2</v>
+      </c>
+      <c r="AD43">
+        <v>25</v>
+      </c>
+      <c r="AE43">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4630,9 +4894,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C53C76-FF94-D249-AA9A-6F4764C599CE}">
   <dimension ref="A1:AA13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -4715,7 +4979,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -4802,7 +5066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -4889,7 +5153,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -4976,7 +5240,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -5063,7 +5327,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -5150,7 +5414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -5237,7 +5501,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -5324,7 +5588,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -5411,7 +5675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -5498,7 +5762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>77</v>
       </c>
@@ -5585,7 +5849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>87</v>
       </c>
@@ -5672,7 +5936,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>88</v>
       </c>

--- a/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
+++ b/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9860f92a834cae8/Belgeler/GitHub/FrequencySliding/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\OneDrive\Belgeler\GitHub\FrequencySliding\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{CD392507-353F-844D-8E7A-EF6D0A11906C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A379D40-2F32-42DE-96F5-B2A9B8BEC40E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F46416-D521-489B-84E9-E811FD3156B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="116">
   <si>
     <t>SubjectID</t>
   </si>
@@ -938,6 +938,12 @@
       <c r="AC2">
         <v>2</v>
       </c>
+      <c r="AD2">
+        <v>33</v>
+      </c>
+      <c r="AE2">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1031,6 +1037,12 @@
       <c r="AC3">
         <v>2</v>
       </c>
+      <c r="AD3">
+        <v>9</v>
+      </c>
+      <c r="AE3">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1223,8 +1235,8 @@
       <c r="AC5">
         <v>1</v>
       </c>
-      <c r="AD5" t="s">
-        <v>50</v>
+      <c r="AD5">
+        <v>9</v>
       </c>
       <c r="AE5">
         <v>12</v>
@@ -1322,6 +1334,12 @@
       <c r="AC6">
         <v>2</v>
       </c>
+      <c r="AD6">
+        <v>7</v>
+      </c>
+      <c r="AE6">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1415,6 +1433,12 @@
       <c r="AC7">
         <v>2</v>
       </c>
+      <c r="AD7">
+        <v>15</v>
+      </c>
+      <c r="AE7">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1508,6 +1532,12 @@
       <c r="AC8">
         <v>2</v>
       </c>
+      <c r="AD8">
+        <v>26</v>
+      </c>
+      <c r="AE8">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1997,8 +2027,8 @@
       <c r="AC13">
         <v>1</v>
       </c>
-      <c r="AD13" t="s">
-        <v>50</v>
+      <c r="AD13">
+        <v>5</v>
       </c>
       <c r="AE13">
         <v>12</v>
@@ -2096,6 +2126,12 @@
       <c r="AC14">
         <v>2</v>
       </c>
+      <c r="AD14">
+        <v>15</v>
+      </c>
+      <c r="AE14">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -2387,6 +2423,12 @@
       <c r="AC17">
         <v>1</v>
       </c>
+      <c r="AD17">
+        <v>2</v>
+      </c>
+      <c r="AE17">
+        <v>16</v>
+      </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -2678,6 +2720,12 @@
       <c r="AC20">
         <v>2</v>
       </c>
+      <c r="AD20">
+        <v>6</v>
+      </c>
+      <c r="AE20">
+        <v>12</v>
+      </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -2771,6 +2819,12 @@
       <c r="AC21">
         <v>1</v>
       </c>
+      <c r="AD21">
+        <v>25</v>
+      </c>
+      <c r="AE21">
+        <v>18</v>
+      </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -3353,6 +3407,18 @@
         <f t="shared" ref="AA27" si="14">SUM(C27:W27)</f>
         <v>47</v>
       </c>
+      <c r="AB27">
+        <v>41</v>
+      </c>
+      <c r="AC27">
+        <v>2</v>
+      </c>
+      <c r="AD27">
+        <v>9</v>
+      </c>
+      <c r="AE27">
+        <v>18</v>
+      </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -3842,8 +3908,8 @@
       <c r="AC32">
         <v>2</v>
       </c>
-      <c r="AD32" t="s">
-        <v>50</v>
+      <c r="AD32">
+        <v>40</v>
       </c>
       <c r="AE32">
         <v>8</v>
@@ -4034,6 +4100,18 @@
         <f>SUM(C34:W34)</f>
         <v>42</v>
       </c>
+      <c r="AB34">
+        <v>34</v>
+      </c>
+      <c r="AC34">
+        <v>2</v>
+      </c>
+      <c r="AD34">
+        <v>12</v>
+      </c>
+      <c r="AE34">
+        <v>18</v>
+      </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
@@ -4319,6 +4397,18 @@
         <f t="shared" si="8"/>
         <v>37</v>
       </c>
+      <c r="AB37">
+        <v>45</v>
+      </c>
+      <c r="AC37">
+        <v>2</v>
+      </c>
+      <c r="AD37">
+        <v>16</v>
+      </c>
+      <c r="AE37">
+        <v>18</v>
+      </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -4505,6 +4595,18 @@
         <f>SUM(C39:W39)</f>
         <v>23</v>
       </c>
+      <c r="AB39">
+        <v>37</v>
+      </c>
+      <c r="AC39">
+        <v>2</v>
+      </c>
+      <c r="AD39">
+        <v>14</v>
+      </c>
+      <c r="AE39">
+        <v>16</v>
+      </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -4591,6 +4693,18 @@
       <c r="AA40">
         <f t="shared" ref="AA40" si="15">SUM(C40:W40)</f>
         <v>53</v>
+      </c>
+      <c r="AB40">
+        <v>18</v>
+      </c>
+      <c r="AC40">
+        <v>2</v>
+      </c>
+      <c r="AD40">
+        <v>5</v>
+      </c>
+      <c r="AE40">
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.3">

--- a/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
+++ b/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\OneDrive\Belgeler\GitHub\FrequencySliding\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaankeskin/projects/FrequencySliding/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F46416-D521-489B-84E9-E811FD3156B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14650DCF-4D87-C249-96B5-F054E5B1E613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BDI-II Multi" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="116">
   <si>
     <t>SubjectID</t>
   </si>
@@ -746,12 +746,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE43"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -846,7 +846,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -945,7 +945,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>100</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>65</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>102</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>104</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>106</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>108</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>81</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>83</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="W34">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X34" cm="1">
         <f t="array" ref="X34">SUM(INDEX(C34:W34, {1,2,3,5,6,7,8,9,10,14}))</f>
@@ -4094,11 +4094,11 @@
       </c>
       <c r="Z34" cm="1">
         <f t="array" ref="Z34">SUM(INDEX(C34:W34, {15,16,18,20,21}))</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AA34">
         <f>SUM(C34:W34)</f>
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AB34">
         <v>34</v>
@@ -4113,7 +4113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -5007,10 +5007,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C53C76-FF94-D249-AA9A-6F4764C599CE}">
-  <dimension ref="A1:AA13"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -5176,11 +5176,11 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <f t="shared" ref="AA2:AA13" si="0">SUM(C2:W2)</f>
+        <f t="shared" ref="AA2:AA14" si="0">SUM(C2:W2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -5789,7 +5789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -5876,12 +5876,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -5917,22 +5917,22 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -5941,163 +5941,175 @@
         <v>0</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" cm="1">
         <f t="array" ref="X11">SUM(INDEX(C11:W11, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y11" cm="1">
         <f t="array" ref="Y11">SUM(INDEX(C11:W11, {4,11,12,13,17,19}))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z11" cm="1">
         <f t="array" ref="Z11">SUM(INDEX(C11:W11, {15,16,18,20,21}))</f>
         <v>2</v>
       </c>
       <c r="AA11">
+        <f>SUM(C11:W11)</f>
+        <v>8</v>
+      </c>
+      <c r="AB11">
+        <v>34</v>
+      </c>
+      <c r="AC11">
+        <v>2</v>
+      </c>
+      <c r="AD11">
+        <v>12</v>
+      </c>
+      <c r="AE11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12" cm="1">
+        <f t="array" ref="X12">SUM(INDEX(C12:W12, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>1</v>
+      </c>
+      <c r="Y12" cm="1">
+        <f t="array" ref="Y12">SUM(INDEX(C12:W12, {4,11,12,13,17,19}))</f>
+        <v>1</v>
+      </c>
+      <c r="Z12" cm="1">
+        <f t="array" ref="Z12">SUM(INDEX(C12:W12, {15,16,18,20,21}))</f>
+        <v>2</v>
+      </c>
+      <c r="AA12">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>87</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>46</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="S12">
-        <v>1</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>2</v>
-      </c>
-      <c r="W12">
-        <v>2</v>
-      </c>
-      <c r="X12" cm="1">
-        <f t="array" ref="X12">SUM(INDEX(C12:W12, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>2</v>
-      </c>
-      <c r="Y12" cm="1">
-        <f t="array" ref="Y12">SUM(INDEX(C12:W12, {4,11,12,13,17,19}))</f>
-        <v>5</v>
-      </c>
-      <c r="Z12" cm="1">
-        <f t="array" ref="Z12">SUM(INDEX(C12:W12, {15,16,18,20,21}))</f>
-        <v>6</v>
-      </c>
-      <c r="AA12">
-        <f>SUM(C12:W12)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>1</v>
@@ -6106,7 +6118,7 @@
         <v>1</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -6115,24 +6127,111 @@
         <v>0</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X13" cm="1">
         <f t="array" ref="X13">SUM(INDEX(C13:W13, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y13" cm="1">
         <f t="array" ref="Y13">SUM(INDEX(C13:W13, {4,11,12,13,17,19}))</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z13" cm="1">
         <f t="array" ref="Z13">SUM(INDEX(C13:W13, {15,16,18,20,21}))</f>
         <v>6</v>
       </c>
       <c r="AA13">
+        <f>SUM(C13:W13)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>3</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>3</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>2</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>3</v>
+      </c>
+      <c r="X14" cm="1">
+        <f t="array" ref="X14">SUM(INDEX(C14:W14, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>20</v>
+      </c>
+      <c r="Y14" cm="1">
+        <f t="array" ref="Y14">SUM(INDEX(C14:W14, {4,11,12,13,17,19}))</f>
+        <v>9</v>
+      </c>
+      <c r="Z14" cm="1">
+        <f t="array" ref="Z14">SUM(INDEX(C14:W14, {15,16,18,20,21}))</f>
+        <v>6</v>
+      </c>
+      <c r="AA14">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>

--- a/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
+++ b/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaankeskin/projects/FrequencySliding/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14650DCF-4D87-C249-96B5-F054E5B1E613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5626C875-17C6-B343-B8B3-4BF3F71DBE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BDI-II Multi" sheetId="1" r:id="rId1"/>
     <sheet name="BDI-II_AfterECT" sheetId="2" r:id="rId2"/>
+    <sheet name="Moca_preECT" sheetId="4" r:id="rId3"/>
+    <sheet name="Moca_postECT" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="142">
   <si>
     <t>SubjectID</t>
   </si>
@@ -404,6 +406,84 @@
   </si>
   <si>
     <t>Education</t>
+  </si>
+  <si>
+    <t>Trail Making</t>
+  </si>
+  <si>
+    <t>Cube Copy</t>
+  </si>
+  <si>
+    <t>Clock Drawing</t>
+  </si>
+  <si>
+    <t>Naming</t>
+  </si>
+  <si>
+    <t>Delayed Recall</t>
+  </si>
+  <si>
+    <t>Digit Span Fwd</t>
+  </si>
+  <si>
+    <t>Digit Span Back</t>
+  </si>
+  <si>
+    <t>Vigilance</t>
+  </si>
+  <si>
+    <t>Serial 7s</t>
+  </si>
+  <si>
+    <t>Sentence Repetition</t>
+  </si>
+  <si>
+    <t>Verbal Fluency</t>
+  </si>
+  <si>
+    <t>Abstraction</t>
+  </si>
+  <si>
+    <t>Orientation Date</t>
+  </si>
+  <si>
+    <t>Orientation Place</t>
+  </si>
+  <si>
+    <t>Education Years</t>
+  </si>
+  <si>
+    <t>Visuospatial Exec</t>
+  </si>
+  <si>
+    <t>Naming Score</t>
+  </si>
+  <si>
+    <t>Memory</t>
+  </si>
+  <si>
+    <t>Attention</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Abstraction Score</t>
+  </si>
+  <si>
+    <t>Orientation</t>
+  </si>
+  <si>
+    <t>Total Raw</t>
+  </si>
+  <si>
+    <t>Education Correction</t>
+  </si>
+  <si>
+    <t>Total Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -6239,4 +6319,2603 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5961F868-A238-EA43-87E5-9D82D76CAD00}">
+  <dimension ref="A1:AA18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" t="s">
+        <v>126</v>
+      </c>
+      <c r="N1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O1" t="s">
+        <v>128</v>
+      </c>
+      <c r="P1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>130</v>
+      </c>
+      <c r="R1" t="s">
+        <v>131</v>
+      </c>
+      <c r="S1" t="s">
+        <v>132</v>
+      </c>
+      <c r="T1" t="s">
+        <v>133</v>
+      </c>
+      <c r="U1" t="s">
+        <v>134</v>
+      </c>
+      <c r="V1" t="s">
+        <v>135</v>
+      </c>
+      <c r="W1" t="s">
+        <v>136</v>
+      </c>
+      <c r="X1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>3</v>
+      </c>
+      <c r="P2">
+        <v>3</v>
+      </c>
+      <c r="Q2">
+        <v>16</v>
+      </c>
+      <c r="R2" cm="1">
+        <f t="array" ref="R2">SUM(INDEX(C2:X2, {1,2,3}))</f>
+        <v>5</v>
+      </c>
+      <c r="S2" cm="1">
+        <f t="array" ref="S2">SUM(INDEX(C2:X2, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T2" cm="1">
+        <f t="array" ref="T2">SUM(INDEX(C2:X2, {5}))</f>
+        <v>2</v>
+      </c>
+      <c r="U2" cm="1">
+        <f t="array" ref="U2">SUM(INDEX(C2:X2, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V2" cm="1">
+        <f t="array" ref="V2">SUM(INDEX(C2:X2, {10,11}))</f>
+        <v>1</v>
+      </c>
+      <c r="W2" cm="1">
+        <f t="array" ref="W2">SUM(INDEX(C2:X2, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X2" cm="1">
+        <f t="array" ref="X2">SUM(INDEX(C2:X2, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y2">
+        <f>SUM(R2:X2)</f>
+        <v>25</v>
+      </c>
+      <c r="Z2">
+        <f>IF(Q2&lt;=12,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f>Y2+Z2</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3">
+        <v>3</v>
+      </c>
+      <c r="Q3">
+        <v>16</v>
+      </c>
+      <c r="R3" cm="1">
+        <f t="array" ref="R3">SUM(INDEX(C3:X3, {1,2,3}))</f>
+        <v>3</v>
+      </c>
+      <c r="S3" cm="1">
+        <f t="array" ref="S3">SUM(INDEX(C3:X3, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T3" cm="1">
+        <f t="array" ref="T3">SUM(INDEX(C3:X3, {5}))</f>
+        <v>0</v>
+      </c>
+      <c r="U3" cm="1">
+        <f t="array" ref="U3">SUM(INDEX(C3:X3, {6,7,8,9}))</f>
+        <v>5</v>
+      </c>
+      <c r="V3" cm="1">
+        <f t="array" ref="V3">SUM(INDEX(C3:X3, {10,11}))</f>
+        <v>3</v>
+      </c>
+      <c r="W3" cm="1">
+        <f t="array" ref="W3">SUM(INDEX(C3:X3, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X3" cm="1">
+        <f t="array" ref="X3">SUM(INDEX(C3:X3, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" ref="Y3:Y13" si="0">SUM(R3:X3)</f>
+        <v>22</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" ref="Z3:Z14" si="1">IF(Q3&lt;=12,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" ref="AA3:AA13" si="2">Y3+Z3</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
+      </c>
+      <c r="Q4">
+        <v>8</v>
+      </c>
+      <c r="R4" cm="1">
+        <f t="array" ref="R4">SUM(INDEX(C4:X4, {1,2,3}))</f>
+        <v>3</v>
+      </c>
+      <c r="S4" cm="1">
+        <f t="array" ref="S4">SUM(INDEX(C4:X4, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T4" cm="1">
+        <f t="array" ref="T4">SUM(INDEX(C4:X4, {5}))</f>
+        <v>0</v>
+      </c>
+      <c r="U4" cm="1">
+        <f t="array" ref="U4">SUM(INDEX(C4:X4, {6,7,8,9}))</f>
+        <v>2</v>
+      </c>
+      <c r="V4" cm="1">
+        <f t="array" ref="V4">SUM(INDEX(C4:X4, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W4" cm="1">
+        <f t="array" ref="W4">SUM(INDEX(C4:X4, {12}))</f>
+        <v>1</v>
+      </c>
+      <c r="X4" cm="1">
+        <f t="array" ref="X4">SUM(INDEX(C4:X4, {13,14}))</f>
+        <v>3</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5">
+        <v>12</v>
+      </c>
+      <c r="R5" cm="1">
+        <f t="array" ref="R5">SUM(INDEX(C5:X5, {1,2,3}))</f>
+        <v>2</v>
+      </c>
+      <c r="S5" cm="1">
+        <f t="array" ref="S5">SUM(INDEX(C5:X5, {4}))</f>
+        <v>1</v>
+      </c>
+      <c r="T5" cm="1">
+        <f t="array" ref="T5">SUM(INDEX(C5:X5, {5}))</f>
+        <v>1</v>
+      </c>
+      <c r="U5" cm="1">
+        <f t="array" ref="U5">SUM(INDEX(C5:X5, {6,7,8,9}))</f>
+        <v>1</v>
+      </c>
+      <c r="V5" cm="1">
+        <f t="array" ref="V5">SUM(INDEX(C5:X5, {10,11}))</f>
+        <v>0</v>
+      </c>
+      <c r="W5" cm="1">
+        <f t="array" ref="W5">SUM(INDEX(C5:X5, {12}))</f>
+        <v>0</v>
+      </c>
+      <c r="X5" cm="1">
+        <f t="array" ref="X5">SUM(INDEX(C5:X5, {13,14}))</f>
+        <v>4</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <v>13</v>
+      </c>
+      <c r="R6" cm="1">
+        <f t="array" ref="R6">SUM(INDEX(C6:X6, {1,2,3}))</f>
+        <v>4</v>
+      </c>
+      <c r="S6" cm="1">
+        <f t="array" ref="S6">SUM(INDEX(C6:X6, {4}))</f>
+        <v>2</v>
+      </c>
+      <c r="T6" cm="1">
+        <f t="array" ref="T6">SUM(INDEX(C6:X6, {5}))</f>
+        <v>0</v>
+      </c>
+      <c r="U6" cm="1">
+        <f t="array" ref="U6">SUM(INDEX(C6:X6, {6,7,8,9}))</f>
+        <v>5</v>
+      </c>
+      <c r="V6" cm="1">
+        <f t="array" ref="V6">SUM(INDEX(C6:X6, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W6" cm="1">
+        <f t="array" ref="W6">SUM(INDEX(C6:X6, {12}))</f>
+        <v>1</v>
+      </c>
+      <c r="X6" cm="1">
+        <f t="array" ref="X6">SUM(INDEX(C6:X6, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
+      </c>
+      <c r="Q7">
+        <v>18</v>
+      </c>
+      <c r="R7" cm="1">
+        <f t="array" ref="R7">SUM(INDEX(C7:X7, {1,2,3}))</f>
+        <v>4</v>
+      </c>
+      <c r="S7" cm="1">
+        <f t="array" ref="S7">SUM(INDEX(C7:X7, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T7" cm="1">
+        <f t="array" ref="T7">SUM(INDEX(C7:X7, {5}))</f>
+        <v>4</v>
+      </c>
+      <c r="U7" cm="1">
+        <f t="array" ref="U7">SUM(INDEX(C7:X7, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V7" cm="1">
+        <f t="array" ref="V7">SUM(INDEX(C7:X7, {10,11}))</f>
+        <v>3</v>
+      </c>
+      <c r="W7" cm="1">
+        <f t="array" ref="W7">SUM(INDEX(C7:X7, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X7" cm="1">
+        <f t="array" ref="X7">SUM(INDEX(C7:X7, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="P8">
+        <v>3</v>
+      </c>
+      <c r="Q8">
+        <v>14</v>
+      </c>
+      <c r="R8" cm="1">
+        <f t="array" ref="R8">SUM(INDEX(C8:X8, {1,2,3}))</f>
+        <v>3</v>
+      </c>
+      <c r="S8" cm="1">
+        <f t="array" ref="S8">SUM(INDEX(C8:X8, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T8" cm="1">
+        <f t="array" ref="T8">SUM(INDEX(C8:X8, {5}))</f>
+        <v>0</v>
+      </c>
+      <c r="U8" cm="1">
+        <f t="array" ref="U8">SUM(INDEX(C8:X8, {6,7,8,9}))</f>
+        <v>4</v>
+      </c>
+      <c r="V8" cm="1">
+        <f t="array" ref="V8">SUM(INDEX(C8:X8, {10,11}))</f>
+        <v>0</v>
+      </c>
+      <c r="W8" cm="1">
+        <f t="array" ref="W8">SUM(INDEX(C8:X8, {12}))</f>
+        <v>0</v>
+      </c>
+      <c r="X8" cm="1">
+        <f t="array" ref="X8">SUM(INDEX(C8:X8, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9">
+        <v>3</v>
+      </c>
+      <c r="P9">
+        <v>3</v>
+      </c>
+      <c r="Q9">
+        <v>16</v>
+      </c>
+      <c r="R9" cm="1">
+        <f t="array" ref="R9">SUM(INDEX(C9:X9, {1,2,3}))</f>
+        <v>3</v>
+      </c>
+      <c r="S9" cm="1">
+        <f t="array" ref="S9">SUM(INDEX(C9:X9, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T9" cm="1">
+        <f t="array" ref="T9">SUM(INDEX(C9:X9, {5}))</f>
+        <v>0</v>
+      </c>
+      <c r="U9" cm="1">
+        <f t="array" ref="U9">SUM(INDEX(C9:X9, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V9" cm="1">
+        <f t="array" ref="V9">SUM(INDEX(C9:X9, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W9" cm="1">
+        <f t="array" ref="W9">SUM(INDEX(C9:X9, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X9" cm="1">
+        <f t="array" ref="X9">SUM(INDEX(C9:X9, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" t="s">
+        <v>50</v>
+      </c>
+      <c r="L10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" t="s">
+        <v>50</v>
+      </c>
+      <c r="P10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R10" t="s">
+        <v>50</v>
+      </c>
+      <c r="S10" t="s">
+        <v>50</v>
+      </c>
+      <c r="T10" t="s">
+        <v>50</v>
+      </c>
+      <c r="U10" t="s">
+        <v>50</v>
+      </c>
+      <c r="V10" t="s">
+        <v>50</v>
+      </c>
+      <c r="W10" t="s">
+        <v>50</v>
+      </c>
+      <c r="X10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>3</v>
+      </c>
+      <c r="Q11">
+        <v>16</v>
+      </c>
+      <c r="R11" cm="1">
+        <f t="array" ref="R11">SUM(INDEX(C11:X11, {1,2,3}))</f>
+        <v>5</v>
+      </c>
+      <c r="S11" cm="1">
+        <f t="array" ref="S11">SUM(INDEX(C11:X11, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T11" cm="1">
+        <f t="array" ref="T11">SUM(INDEX(C11:X11, {5}))</f>
+        <v>3</v>
+      </c>
+      <c r="U11" cm="1">
+        <f t="array" ref="U11">SUM(INDEX(C11:X11, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V11" cm="1">
+        <f t="array" ref="V11">SUM(INDEX(C11:X11, {10,11}))</f>
+        <v>3</v>
+      </c>
+      <c r="W11" cm="1">
+        <f t="array" ref="W11">SUM(INDEX(C11:X11, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X11" cm="1">
+        <f t="array" ref="X11">SUM(INDEX(C11:X11, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12">
+        <v>16</v>
+      </c>
+      <c r="R12" cm="1">
+        <f t="array" ref="R12">SUM(INDEX(C12:X12, {1,2,3}))</f>
+        <v>3</v>
+      </c>
+      <c r="S12" cm="1">
+        <f t="array" ref="S12">SUM(INDEX(C12:X12, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T12" cm="1">
+        <f t="array" ref="T12">SUM(INDEX(C12:X12, {5}))</f>
+        <v>2</v>
+      </c>
+      <c r="U12" cm="1">
+        <f t="array" ref="U12">SUM(INDEX(C12:X12, {6,7,8,9}))</f>
+        <v>3</v>
+      </c>
+      <c r="V12" cm="1">
+        <f t="array" ref="V12">SUM(INDEX(C12:X12, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W12" cm="1">
+        <f t="array" ref="W12">SUM(INDEX(C12:X12, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X12" cm="1">
+        <f t="array" ref="X12">SUM(INDEX(C12:X12, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y12">
+        <f>SUM(R12:X12)</f>
+        <v>21</v>
+      </c>
+      <c r="Z12">
+        <f>IF(Q12&lt;=12,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <f>Y12+Z12</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13">
+        <v>3</v>
+      </c>
+      <c r="P13">
+        <v>3</v>
+      </c>
+      <c r="Q13">
+        <v>16</v>
+      </c>
+      <c r="R13" cm="1">
+        <f t="array" ref="R13">SUM(INDEX(C13:X13, {1,2,3}))</f>
+        <v>0</v>
+      </c>
+      <c r="S13" cm="1">
+        <f t="array" ref="S13">SUM(INDEX(C13:X13, {4}))</f>
+        <v>0</v>
+      </c>
+      <c r="T13" cm="1">
+        <f t="array" ref="T13">SUM(INDEX(C13:X13, {5}))</f>
+        <v>1</v>
+      </c>
+      <c r="U13" cm="1">
+        <f t="array" ref="U13">SUM(INDEX(C13:X13, {6,7,8,9}))</f>
+        <v>4</v>
+      </c>
+      <c r="V13" cm="1">
+        <f t="array" ref="V13">SUM(INDEX(C13:X13, {10,11}))</f>
+        <v>3</v>
+      </c>
+      <c r="W13" cm="1">
+        <f t="array" ref="W13">SUM(INDEX(C13:X13, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X13" cm="1">
+        <f t="array" ref="X13">SUM(INDEX(C13:X13, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y13">
+        <f>SUM(R13:X13)</f>
+        <v>16</v>
+      </c>
+      <c r="Z13">
+        <f>IF(Q13&lt;=12,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <f>Y13+Z13</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>3</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>2</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>3</v>
+      </c>
+      <c r="Q14">
+        <v>12</v>
+      </c>
+      <c r="R14" cm="1">
+        <f t="array" ref="R14">SUM(INDEX(C14:X14, {1,2,3}))</f>
+        <v>2</v>
+      </c>
+      <c r="S14" cm="1">
+        <f t="array" ref="S14">SUM(INDEX(C14:X14, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T14" cm="1">
+        <f t="array" ref="T14">SUM(INDEX(C14:X14, {5}))</f>
+        <v>3</v>
+      </c>
+      <c r="U14" cm="1">
+        <f t="array" ref="U14">SUM(INDEX(C14:X14, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V14" cm="1">
+        <f t="array" ref="V14">SUM(INDEX(C14:X14, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W14" cm="1">
+        <f t="array" ref="W14">SUM(INDEX(C14:X14, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X14" cm="1">
+        <f t="array" ref="X14">SUM(INDEX(C14:X14, {13,14}))</f>
+        <v>5</v>
+      </c>
+      <c r="Y14">
+        <f>SUM(R14:X14)</f>
+        <v>23</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <f>Y14+Z14</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA394A0-E846-1341-BEEC-C2F40712C84E}">
+  <dimension ref="A1:AA14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" t="s">
+        <v>126</v>
+      </c>
+      <c r="N1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O1" t="s">
+        <v>128</v>
+      </c>
+      <c r="P1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>130</v>
+      </c>
+      <c r="R1" t="s">
+        <v>131</v>
+      </c>
+      <c r="S1" t="s">
+        <v>132</v>
+      </c>
+      <c r="T1" t="s">
+        <v>133</v>
+      </c>
+      <c r="U1" t="s">
+        <v>134</v>
+      </c>
+      <c r="V1" t="s">
+        <v>135</v>
+      </c>
+      <c r="W1" t="s">
+        <v>136</v>
+      </c>
+      <c r="X1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>3</v>
+      </c>
+      <c r="P2">
+        <v>3</v>
+      </c>
+      <c r="Q2">
+        <v>16</v>
+      </c>
+      <c r="R2" cm="1">
+        <f t="array" ref="R2">SUM(INDEX(C2:X2, {1,2,3}))</f>
+        <v>5</v>
+      </c>
+      <c r="S2" cm="1">
+        <f t="array" ref="S2">SUM(INDEX(C2:X2, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T2" cm="1">
+        <f t="array" ref="T2">SUM(INDEX(C2:X2, {5}))</f>
+        <v>2</v>
+      </c>
+      <c r="U2" cm="1">
+        <f t="array" ref="U2">SUM(INDEX(C2:X2, {6,7,8,9}))</f>
+        <v>5</v>
+      </c>
+      <c r="V2" cm="1">
+        <f t="array" ref="V2">SUM(INDEX(C2:X2, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W2" cm="1">
+        <f t="array" ref="W2">SUM(INDEX(C2:X2, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X2" cm="1">
+        <f t="array" ref="X2">SUM(INDEX(C2:X2, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y2">
+        <f>SUM(R2:X2)</f>
+        <v>25</v>
+      </c>
+      <c r="Z2">
+        <f>IF(Q2&lt;=12,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f>Y2+Z2</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3">
+        <v>3</v>
+      </c>
+      <c r="Q3">
+        <v>16</v>
+      </c>
+      <c r="R3" cm="1">
+        <f t="array" ref="R3">SUM(INDEX(C3:X3, {1,2,3}))</f>
+        <v>2</v>
+      </c>
+      <c r="S3" cm="1">
+        <f t="array" ref="S3">SUM(INDEX(C3:X3, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T3" cm="1">
+        <f t="array" ref="T3">SUM(INDEX(C3:X3, {5}))</f>
+        <v>0</v>
+      </c>
+      <c r="U3" cm="1">
+        <f t="array" ref="U3">SUM(INDEX(C3:X3, {6,7,8,9}))</f>
+        <v>5</v>
+      </c>
+      <c r="V3" cm="1">
+        <f t="array" ref="V3">SUM(INDEX(C3:X3, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W3" cm="1">
+        <f t="array" ref="W3">SUM(INDEX(C3:X3, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X3" cm="1">
+        <f t="array" ref="X3">SUM(INDEX(C3:X3, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" ref="Y3:Y14" si="0">SUM(R3:X3)</f>
+        <v>20</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" ref="Z3:Z14" si="1">IF(Q3&lt;=12,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" ref="AA3:AA14" si="2">Y3+Z3</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="P4">
+        <v>3</v>
+      </c>
+      <c r="Q4">
+        <v>8</v>
+      </c>
+      <c r="R4" cm="1">
+        <f t="array" ref="R4">SUM(INDEX(C4:X4, {1,2,3}))</f>
+        <v>4</v>
+      </c>
+      <c r="S4" cm="1">
+        <f t="array" ref="S4">SUM(INDEX(C4:X4, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T4" cm="1">
+        <f t="array" ref="T4">SUM(INDEX(C4:X4, {5}))</f>
+        <v>2</v>
+      </c>
+      <c r="U4" cm="1">
+        <f t="array" ref="U4">SUM(INDEX(C4:X4, {6,7,8,9}))</f>
+        <v>4</v>
+      </c>
+      <c r="V4" cm="1">
+        <f t="array" ref="V4">SUM(INDEX(C4:X4, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W4" cm="1">
+        <f t="array" ref="W4">SUM(INDEX(C4:X4, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X4" cm="1">
+        <f t="array" ref="X4">SUM(INDEX(C4:X4, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>3</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5">
+        <v>12</v>
+      </c>
+      <c r="R5" cm="1">
+        <f t="array" ref="R5">SUM(INDEX(C5:X5, {1,2,3}))</f>
+        <v>4</v>
+      </c>
+      <c r="S5" cm="1">
+        <f t="array" ref="S5">SUM(INDEX(C5:X5, {4}))</f>
+        <v>2</v>
+      </c>
+      <c r="T5" cm="1">
+        <f t="array" ref="T5">SUM(INDEX(C5:X5, {5}))</f>
+        <v>3</v>
+      </c>
+      <c r="U5" cm="1">
+        <f t="array" ref="U5">SUM(INDEX(C5:X5, {6,7,8,9}))</f>
+        <v>3</v>
+      </c>
+      <c r="V5" cm="1">
+        <f t="array" ref="V5">SUM(INDEX(C5:X5, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W5" cm="1">
+        <f t="array" ref="W5">SUM(INDEX(C5:X5, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X5" cm="1">
+        <f t="array" ref="X5">SUM(INDEX(C5:X5, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <v>13</v>
+      </c>
+      <c r="R6" cm="1">
+        <f t="array" ref="R6">SUM(INDEX(C6:X6, {1,2,3}))</f>
+        <v>3</v>
+      </c>
+      <c r="S6" cm="1">
+        <f t="array" ref="S6">SUM(INDEX(C6:X6, {4}))</f>
+        <v>2</v>
+      </c>
+      <c r="T6" cm="1">
+        <f t="array" ref="T6">SUM(INDEX(C6:X6, {5}))</f>
+        <v>0</v>
+      </c>
+      <c r="U6" cm="1">
+        <f t="array" ref="U6">SUM(INDEX(C6:X6, {6,7,8,9}))</f>
+        <v>2</v>
+      </c>
+      <c r="V6" cm="1">
+        <f t="array" ref="V6">SUM(INDEX(C6:X6, {10,11}))</f>
+        <v>1</v>
+      </c>
+      <c r="W6" cm="1">
+        <f t="array" ref="W6">SUM(INDEX(C6:X6, {12}))</f>
+        <v>1</v>
+      </c>
+      <c r="X6" cm="1">
+        <f t="array" ref="X6">SUM(INDEX(C6:X6, {13,14}))</f>
+        <v>5</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
+      </c>
+      <c r="Q7">
+        <v>18</v>
+      </c>
+      <c r="R7" cm="1">
+        <f t="array" ref="R7">SUM(INDEX(C7:X7, {1,2,3}))</f>
+        <v>4</v>
+      </c>
+      <c r="S7" cm="1">
+        <f t="array" ref="S7">SUM(INDEX(C7:X7, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T7" cm="1">
+        <f t="array" ref="T7">SUM(INDEX(C7:X7, {5}))</f>
+        <v>1</v>
+      </c>
+      <c r="U7" cm="1">
+        <f t="array" ref="U7">SUM(INDEX(C7:X7, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V7" cm="1">
+        <f t="array" ref="V7">SUM(INDEX(C7:X7, {10,11}))</f>
+        <v>3</v>
+      </c>
+      <c r="W7" cm="1">
+        <f t="array" ref="W7">SUM(INDEX(C7:X7, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X7" cm="1">
+        <f t="array" ref="X7">SUM(INDEX(C7:X7, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="P8">
+        <v>3</v>
+      </c>
+      <c r="Q8">
+        <v>14</v>
+      </c>
+      <c r="R8" cm="1">
+        <f t="array" ref="R8">SUM(INDEX(C8:X8, {1,2,3}))</f>
+        <v>3</v>
+      </c>
+      <c r="S8" cm="1">
+        <f t="array" ref="S8">SUM(INDEX(C8:X8, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T8" cm="1">
+        <f t="array" ref="T8">SUM(INDEX(C8:X8, {5}))</f>
+        <v>0</v>
+      </c>
+      <c r="U8" cm="1">
+        <f t="array" ref="U8">SUM(INDEX(C8:X8, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V8" cm="1">
+        <f t="array" ref="V8">SUM(INDEX(C8:X8, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W8" cm="1">
+        <f t="array" ref="W8">SUM(INDEX(C8:X8, {12}))</f>
+        <v>0</v>
+      </c>
+      <c r="X8" cm="1">
+        <f t="array" ref="X8">SUM(INDEX(C8:X8, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9">
+        <v>3</v>
+      </c>
+      <c r="P9">
+        <v>3</v>
+      </c>
+      <c r="Q9">
+        <v>16</v>
+      </c>
+      <c r="R9" cm="1">
+        <f t="array" ref="R9">SUM(INDEX(C9:X9, {1,2,3}))</f>
+        <v>4</v>
+      </c>
+      <c r="S9" cm="1">
+        <f t="array" ref="S9">SUM(INDEX(C9:X9, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T9" cm="1">
+        <f t="array" ref="T9">SUM(INDEX(C9:X9, {5}))</f>
+        <v>5</v>
+      </c>
+      <c r="U9" cm="1">
+        <f t="array" ref="U9">SUM(INDEX(C9:X9, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V9" cm="1">
+        <f t="array" ref="V9">SUM(INDEX(C9:X9, {10,11}))</f>
+        <v>3</v>
+      </c>
+      <c r="W9" cm="1">
+        <f t="array" ref="W9">SUM(INDEX(C9:X9, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X9" cm="1">
+        <f t="array" ref="X9">SUM(INDEX(C9:X9, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10">
+        <v>8</v>
+      </c>
+      <c r="R10" cm="1">
+        <f t="array" ref="R10">SUM(INDEX(C10:X10, {1,2,3}))</f>
+        <v>4</v>
+      </c>
+      <c r="S10" cm="1">
+        <f t="array" ref="S10">SUM(INDEX(C10:X10, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T10" cm="1">
+        <f t="array" ref="T10">SUM(INDEX(C10:X10, {5}))</f>
+        <v>4</v>
+      </c>
+      <c r="U10" cm="1">
+        <f t="array" ref="U10">SUM(INDEX(C10:X10, {6,7,8,9}))</f>
+        <v>2</v>
+      </c>
+      <c r="V10" cm="1">
+        <f t="array" ref="V10">SUM(INDEX(C10:X10, {10,11}))</f>
+        <v>1</v>
+      </c>
+      <c r="W10" cm="1">
+        <f t="array" ref="W10">SUM(INDEX(C10:X10, {12}))</f>
+        <v>0</v>
+      </c>
+      <c r="X10" cm="1">
+        <f t="array" ref="X10">SUM(INDEX(C10:X10, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>3</v>
+      </c>
+      <c r="Q11">
+        <v>16</v>
+      </c>
+      <c r="R11" cm="1">
+        <f t="array" ref="R11">SUM(INDEX(C11:X11, {1,2,3}))</f>
+        <v>5</v>
+      </c>
+      <c r="S11" cm="1">
+        <f t="array" ref="S11">SUM(INDEX(C11:X11, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T11" cm="1">
+        <f t="array" ref="T11">SUM(INDEX(C11:X11, {5}))</f>
+        <v>1</v>
+      </c>
+      <c r="U11" cm="1">
+        <f t="array" ref="U11">SUM(INDEX(C11:X11, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V11" cm="1">
+        <f t="array" ref="V11">SUM(INDEX(C11:X11, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W11" cm="1">
+        <f t="array" ref="W11">SUM(INDEX(C11:X11, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X11" cm="1">
+        <f t="array" ref="X11">SUM(INDEX(C11:X11, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12">
+        <v>16</v>
+      </c>
+      <c r="R12" cm="1">
+        <f t="array" ref="R12">SUM(INDEX(C12:X12, {1,2,3}))</f>
+        <v>4</v>
+      </c>
+      <c r="S12" cm="1">
+        <f t="array" ref="S12">SUM(INDEX(C12:X12, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T12" cm="1">
+        <f t="array" ref="T12">SUM(INDEX(C12:X12, {5}))</f>
+        <v>1</v>
+      </c>
+      <c r="U12" cm="1">
+        <f t="array" ref="U12">SUM(INDEX(C12:X12, {6,7,8,9}))</f>
+        <v>5</v>
+      </c>
+      <c r="V12" cm="1">
+        <f t="array" ref="V12">SUM(INDEX(C12:X12, {10,11}))</f>
+        <v>3</v>
+      </c>
+      <c r="W12" cm="1">
+        <f t="array" ref="W12">SUM(INDEX(C12:X12, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X12" cm="1">
+        <f t="array" ref="X12">SUM(INDEX(C12:X12, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y12">
+        <f>SUM(R12:X12)</f>
+        <v>24</v>
+      </c>
+      <c r="Z12">
+        <f>IF(Q12&lt;=12,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <f>Y12+Z12</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>3</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13">
+        <v>3</v>
+      </c>
+      <c r="P13">
+        <v>3</v>
+      </c>
+      <c r="Q13">
+        <v>16</v>
+      </c>
+      <c r="R13" cm="1">
+        <f t="array" ref="R13">SUM(INDEX(C13:X13, {1,2,3}))</f>
+        <v>0</v>
+      </c>
+      <c r="S13" cm="1">
+        <f t="array" ref="S13">SUM(INDEX(C13:X13, {4}))</f>
+        <v>0</v>
+      </c>
+      <c r="T13" cm="1">
+        <f t="array" ref="T13">SUM(INDEX(C13:X13, {5}))</f>
+        <v>3</v>
+      </c>
+      <c r="U13" cm="1">
+        <f t="array" ref="U13">SUM(INDEX(C13:X13, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V13" cm="1">
+        <f t="array" ref="V13">SUM(INDEX(C13:X13, {10,11}))</f>
+        <v>3</v>
+      </c>
+      <c r="W13" cm="1">
+        <f t="array" ref="W13">SUM(INDEX(C13:X13, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X13" cm="1">
+        <f t="array" ref="X13">SUM(INDEX(C13:X13, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y13">
+        <f>SUM(R13:X13)</f>
+        <v>20</v>
+      </c>
+      <c r="Z13">
+        <f>IF(Q13&lt;=12,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <f>Y13+Z13</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>3</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>2</v>
+      </c>
+      <c r="O14">
+        <v>3</v>
+      </c>
+      <c r="P14">
+        <v>3</v>
+      </c>
+      <c r="Q14">
+        <v>12</v>
+      </c>
+      <c r="R14" cm="1">
+        <f t="array" ref="R14">SUM(INDEX(C14:X14, {1,2,3}))</f>
+        <v>3</v>
+      </c>
+      <c r="S14" cm="1">
+        <f t="array" ref="S14">SUM(INDEX(C14:X14, {4}))</f>
+        <v>3</v>
+      </c>
+      <c r="T14" cm="1">
+        <f t="array" ref="T14">SUM(INDEX(C14:X14, {5}))</f>
+        <v>3</v>
+      </c>
+      <c r="U14" cm="1">
+        <f t="array" ref="U14">SUM(INDEX(C14:X14, {6,7,8,9}))</f>
+        <v>6</v>
+      </c>
+      <c r="V14" cm="1">
+        <f t="array" ref="V14">SUM(INDEX(C14:X14, {10,11}))</f>
+        <v>2</v>
+      </c>
+      <c r="W14" cm="1">
+        <f t="array" ref="W14">SUM(INDEX(C14:X14, {12}))</f>
+        <v>2</v>
+      </c>
+      <c r="X14" cm="1">
+        <f t="array" ref="X14">SUM(INDEX(C14:X14, {13,14}))</f>
+        <v>6</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
+++ b/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaankeskin/projects/FrequencySliding/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5626C875-17C6-B343-B8B3-4BF3F71DBE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC6E653-CF34-5542-98C6-1F68F9130B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6583,7 +6583,7 @@
         <v>6</v>
       </c>
       <c r="Y3">
-        <f t="shared" ref="Y3:Y13" si="0">SUM(R3:X3)</f>
+        <f t="shared" ref="Y3:Y11" si="0">SUM(R3:X3)</f>
         <v>22</v>
       </c>
       <c r="Z3">
@@ -6591,7 +6591,7 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <f t="shared" ref="AA3:AA13" si="2">Y3+Z3</f>
+        <f t="shared" ref="AA3:AA11" si="2">Y3+Z3</f>
         <v>22</v>
       </c>
     </row>

--- a/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
+++ b/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaankeskin/projects/FrequencySliding/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9860f92a834cae8/Belgeler/GitHub/FrequencySliding/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC6E653-CF34-5542-98C6-1F68F9130B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{AFC6E653-CF34-5542-98C6-1F68F9130B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9BDA4F7-6514-4765-ACD9-8C18711D139F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BDI-II Multi" sheetId="1" r:id="rId1"/>
@@ -826,12 +826,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -926,45 +926,45 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -973,163 +973,163 @@
         <v>1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X2" cm="1">
         <f t="array" ref="X2">SUM(INDEX(C2:W2, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y2" cm="1">
         <f t="array" ref="Y2">SUM(INDEX(C2:W2, {4,11,12,13,17,19}))</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z2" cm="1">
         <f t="array" ref="Z2">SUM(INDEX(C2:W2, {15,16,18,20,21}))</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AA2">
-        <f t="shared" ref="AA2:AA4" si="0">SUM(C2:W2)</f>
-        <v>8</v>
+        <f>SUM(C2:W2)</f>
+        <v>33</v>
       </c>
       <c r="AB2">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="AC2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD2">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="AE2">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3">
         <v>2</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X3" cm="1">
         <f t="array" ref="X3">SUM(INDEX(C3:W3, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="Y3" cm="1">
         <f t="array" ref="Y3">SUM(INDEX(C3:W3, {4,11,12,13,17,19}))</f>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z3" cm="1">
         <f t="array" ref="Z3">SUM(INDEX(C3:W3, {15,16,18,20,21}))</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="0"/>
-        <v>48</v>
+        <f>SUM(C3:W3)</f>
+        <v>27</v>
       </c>
       <c r="AB3">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AC3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE3">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1138,7 +1138,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1147,37 +1147,37 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <v>3</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4">
         <v>3</v>
@@ -1192,110 +1192,110 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X4" cm="1">
         <f t="array" ref="X4">SUM(INDEX(C4:W4, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Y4" cm="1">
         <f t="array" ref="Y4">SUM(INDEX(C4:W4, {4,11,12,13,17,19}))</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z4" cm="1">
         <f t="array" ref="Z4">SUM(INDEX(C4:W4, {15,16,18,20,21}))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="0"/>
-        <v>37</v>
+        <f>SUM(C4:W4)</f>
+        <v>47</v>
       </c>
       <c r="AB4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AC4">
         <v>2</v>
       </c>
       <c r="AD4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE4">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X5" cm="1">
         <f t="array" ref="X5">SUM(INDEX(C5:W5, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="Y5" cm="1">
         <f t="array" ref="Y5">SUM(INDEX(C5:W5, {4,11,12,13,17,19}))</f>
@@ -1303,37 +1303,37 @@
       </c>
       <c r="Z5" cm="1">
         <f t="array" ref="Z5">SUM(INDEX(C5:W5, {15,16,18,20,21}))</f>
+        <v>7</v>
+      </c>
+      <c r="AA5">
+        <f>SUM(C5:W5)</f>
+        <v>40</v>
+      </c>
+      <c r="AB5">
+        <v>43</v>
+      </c>
+      <c r="AC5">
+        <v>2</v>
+      </c>
+      <c r="AD5">
         <v>5</v>
       </c>
-      <c r="AA5">
-        <f t="shared" ref="AA5" si="1">SUM(C5:W5)</f>
-        <v>25</v>
-      </c>
-      <c r="AB5">
-        <v>49</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>9</v>
-      </c>
       <c r="AE5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1345,28 +1345,28 @@
         <v>3</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>3</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N6">
         <v>3</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P6">
         <v>3</v>
@@ -1375,175 +1375,175 @@
         <v>2</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6">
         <v>0</v>
       </c>
       <c r="V6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W6">
         <v>3</v>
       </c>
       <c r="X6" cm="1">
         <f t="array" ref="X6">SUM(INDEX(C6:W6, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Y6" cm="1">
         <f t="array" ref="Y6">SUM(INDEX(C6:W6, {4,11,12,13,17,19}))</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z6" cm="1">
         <f t="array" ref="Z6">SUM(INDEX(C6:W6, {15,16,18,20,21}))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA6">
-        <f t="shared" ref="AA6" si="2">SUM(C6:W6)</f>
-        <v>42</v>
+        <f>SUM(C6:W6)</f>
+        <v>48</v>
       </c>
       <c r="AB6">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AC6">
         <v>2</v>
       </c>
       <c r="AD6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE6">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7">
         <v>1</v>
       </c>
       <c r="X7" cm="1">
         <f t="array" ref="X7">SUM(INDEX(C7:W7, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Y7" cm="1">
         <f t="array" ref="Y7">SUM(INDEX(C7:W7, {4,11,12,13,17,19}))</f>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Z7" cm="1">
         <f t="array" ref="Z7">SUM(INDEX(C7:W7, {15,16,18,20,21}))</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA7">
-        <f t="shared" ref="AA7" si="3">SUM(C7:W7)</f>
-        <v>46</v>
+        <f>SUM(C7:W7)</f>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="AC7">
         <v>2</v>
       </c>
       <c r="AD7">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AE7">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -1552,16 +1552,16 @@
         <v>1</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8">
         <v>2</v>
@@ -1570,184 +1570,184 @@
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X8" cm="1">
         <f t="array" ref="X8">SUM(INDEX(C8:W8, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y8" cm="1">
         <f t="array" ref="Y8">SUM(INDEX(C8:W8, {4,11,12,13,17,19}))</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z8" cm="1">
         <f t="array" ref="Z8">SUM(INDEX(C8:W8, {15,16,18,20,21}))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <f t="shared" ref="AA8" si="4">SUM(C8:W8)</f>
-        <v>35</v>
+        <f>SUM(C8:W8)</f>
+        <v>32</v>
       </c>
       <c r="AB8">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AD8">
+        <v>22</v>
+      </c>
+      <c r="AE8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="AE8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
       <c r="C9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>3</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X9" cm="1">
         <f t="array" ref="X9">SUM(INDEX(C9:W9, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="Y9" cm="1">
         <f t="array" ref="Y9">SUM(INDEX(C9:W9, {4,11,12,13,17,19}))</f>
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Z9" cm="1">
         <f t="array" ref="Z9">SUM(INDEX(C9:W9, {15,16,18,20,21}))</f>
+        <v>3</v>
+      </c>
+      <c r="AA9">
+        <f>SUM(C9:W9)</f>
+        <v>22</v>
+      </c>
+      <c r="AB9">
+        <v>50</v>
+      </c>
+      <c r="AC9">
+        <v>2</v>
+      </c>
+      <c r="AD9">
+        <v>20</v>
+      </c>
+      <c r="AE9">
         <v>14</v>
       </c>
-      <c r="AA9">
-        <f t="shared" ref="AA9" si="5">SUM(C9:W9)</f>
-        <v>54</v>
-      </c>
-      <c r="AB9">
-        <v>20</v>
-      </c>
-      <c r="AC9">
-        <v>2</v>
-      </c>
-      <c r="AD9">
-        <v>6</v>
-      </c>
-      <c r="AE9">
-        <v>12</v>
-      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1756,19 +1756,19 @@
         <v>1</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10">
         <v>2</v>
@@ -1783,46 +1783,46 @@
         <v>0</v>
       </c>
       <c r="V10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" cm="1">
         <f t="array" ref="X10">SUM(INDEX(C10:W10, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y10" cm="1">
         <f t="array" ref="Y10">SUM(INDEX(C10:W10, {4,11,12,13,17,19}))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z10" cm="1">
         <f t="array" ref="Z10">SUM(INDEX(C10:W10, {15,16,18,20,21}))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <f t="shared" ref="AA10:AA11" si="6">SUM(C10:W10)</f>
-        <v>24</v>
+        <f>SUM(C10:W10)</f>
+        <v>19</v>
       </c>
       <c r="AB10">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AC10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD10">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AE10">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -1831,13 +1831,13 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1846,13 +1846,13 @@
         <v>2</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -1861,16 +1861,16 @@
         <v>3</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>2</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11">
         <v>3</v>
@@ -1889,22 +1889,22 @@
       </c>
       <c r="X11" cm="1">
         <f t="array" ref="X11">SUM(INDEX(C11:W11, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Y11" cm="1">
         <f t="array" ref="Y11">SUM(INDEX(C11:W11, {4,11,12,13,17,19}))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z11" cm="1">
         <f t="array" ref="Z11">SUM(INDEX(C11:W11, {15,16,18,20,21}))</f>
         <v>6</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="6"/>
-        <v>30</v>
+        <f>SUM(C11:W11)</f>
+        <v>37</v>
       </c>
       <c r="AB11">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="AC11">
         <v>2</v>
@@ -1916,36 +1916,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1954,103 +1954,103 @@
         <v>3</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12">
         <v>3</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W12">
         <v>3</v>
       </c>
       <c r="X12" cm="1">
         <f t="array" ref="X12">SUM(INDEX(C12:W12, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Y12" cm="1">
         <f t="array" ref="Y12">SUM(INDEX(C12:W12, {4,11,12,13,17,19}))</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z12" cm="1">
         <f t="array" ref="Z12">SUM(INDEX(C12:W12, {15,16,18,20,21}))</f>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA12">
-        <f t="shared" ref="AA12" si="7">SUM(C12:W12)</f>
-        <v>44</v>
+        <f>SUM(C12:W12)</f>
+        <v>25</v>
       </c>
       <c r="AB12">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="AC12">
         <v>1</v>
       </c>
       <c r="AD12">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="AE12">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M13">
         <v>1</v>
@@ -2059,19 +2059,19 @@
         <v>3</v>
       </c>
       <c r="O13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13">
         <v>1</v>
@@ -2080,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X13" cm="1">
         <f t="array" ref="X13">SUM(INDEX(C13:W13, {1,2,3,5,6,7,8,9,10,14}))</f>
@@ -2091,117 +2091,117 @@
       </c>
       <c r="Y13" cm="1">
         <f t="array" ref="Y13">SUM(INDEX(C13:W13, {4,11,12,13,17,19}))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z13" cm="1">
         <f t="array" ref="Z13">SUM(INDEX(C13:W13, {15,16,18,20,21}))</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AA13">
-        <f t="shared" ref="AA13:AA37" si="8">SUM(C13:W13)</f>
-        <v>38</v>
+        <f>SUM(C13:W13)</f>
+        <v>42</v>
       </c>
       <c r="AB13">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AC13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X14" cm="1">
         <f t="array" ref="X14">SUM(INDEX(C14:W14, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="Y14" cm="1">
         <f t="array" ref="Y14">SUM(INDEX(C14:W14, {4,11,12,13,17,19}))</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Z14" cm="1">
         <f t="array" ref="Z14">SUM(INDEX(C14:W14, {15,16,18,20,21}))</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="8"/>
-        <v>22</v>
+        <f>SUM(C14:W14)</f>
+        <v>46</v>
       </c>
       <c r="AB14">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="AC14">
         <v>2</v>
@@ -2210,15 +2210,15 @@
         <v>15</v>
       </c>
       <c r="AE14">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -2227,19 +2227,19 @@
         <v>3</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2248,25 +2248,25 @@
         <v>1</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15">
         <v>1</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2275,17 +2275,17 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X15" cm="1">
         <f t="array" ref="X15">SUM(INDEX(C15:W15, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y15" cm="1">
         <f t="array" ref="Y15">SUM(INDEX(C15:W15, {4,11,12,13,17,19}))</f>
@@ -2293,31 +2293,31 @@
       </c>
       <c r="Z15" cm="1">
         <f t="array" ref="Z15">SUM(INDEX(C15:W15, {15,16,18,20,21}))</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="8"/>
-        <v>27</v>
+        <f>SUM(C15:W15)</f>
+        <v>32</v>
       </c>
       <c r="AB15">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC15">
         <v>2</v>
       </c>
       <c r="AD15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE15">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2326,46 +2326,46 @@
         <v>2</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2377,67 +2377,67 @@
         <v>1</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X16" cm="1">
         <f t="array" ref="X16">SUM(INDEX(C16:W16, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Y16" cm="1">
         <f t="array" ref="Y16">SUM(INDEX(C16:W16, {4,11,12,13,17,19}))</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Z16" cm="1">
         <f t="array" ref="Z16">SUM(INDEX(C16:W16, {15,16,18,20,21}))</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="8"/>
-        <v>10</v>
+        <f>SUM(C16:W16)</f>
+        <v>35</v>
       </c>
       <c r="AB16">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AC16">
         <v>2</v>
       </c>
       <c r="AD16">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AE16">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2446,13 +2446,13 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17">
         <v>2</v>
@@ -2461,19 +2461,19 @@
         <v>1</v>
       </c>
       <c r="Q17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17">
         <v>1</v>
@@ -2483,57 +2483,57 @@
       </c>
       <c r="X17" cm="1">
         <f t="array" ref="X17">SUM(INDEX(C17:W17, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y17" cm="1">
         <f t="array" ref="Y17">SUM(INDEX(C17:W17, {4,11,12,13,17,19}))</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Z17" cm="1">
         <f t="array" ref="Z17">SUM(INDEX(C17:W17, {15,16,18,20,21}))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <f t="shared" ref="AA17" si="9">SUM(C17:W17)</f>
-        <v>25</v>
+        <f>SUM(C17:W17)</f>
+        <v>35</v>
       </c>
       <c r="AB17">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="AC17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD17">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="AE17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>3</v>
@@ -2545,181 +2545,181 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R18">
         <v>1</v>
       </c>
       <c r="S18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X18" cm="1">
         <f t="array" ref="X18">SUM(INDEX(C18:W18, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Y18" cm="1">
         <f t="array" ref="Y18">SUM(INDEX(C18:W18, {4,11,12,13,17,19}))</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z18" cm="1">
         <f t="array" ref="Z18">SUM(INDEX(C18:W18, {15,16,18,20,21}))</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <f t="shared" ref="AA18" si="10">SUM(C18:W18)</f>
-        <v>52</v>
+        <f>SUM(C18:W18)</f>
+        <v>32</v>
       </c>
       <c r="AB18">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="AC18">
         <v>2</v>
       </c>
       <c r="AD18">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AE18">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19">
         <v>2</v>
       </c>
       <c r="N19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X19" cm="1">
         <f t="array" ref="X19">SUM(INDEX(C19:W19, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Y19" cm="1">
         <f t="array" ref="Y19">SUM(INDEX(C19:W19, {4,11,12,13,17,19}))</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Z19" cm="1">
         <f t="array" ref="Z19">SUM(INDEX(C19:W19, {15,16,18,20,21}))</f>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AA19">
-        <f t="shared" ref="AA19" si="11">SUM(C19:W19)</f>
-        <v>25</v>
+        <f>SUM(C19:W19)</f>
+        <v>54</v>
       </c>
       <c r="AB19">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AC19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2728,43 +2728,43 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <v>1</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -2773,46 +2773,46 @@
         <v>0</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X20" cm="1">
         <f t="array" ref="X20">SUM(INDEX(C20:W20, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y20" cm="1">
         <f t="array" ref="Y20">SUM(INDEX(C20:W20, {4,11,12,13,17,19}))</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z20" cm="1">
         <f t="array" ref="Z20">SUM(INDEX(C20:W20, {15,16,18,20,21}))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA20">
-        <f t="shared" ref="AA20" si="12">SUM(C20:W20)</f>
-        <v>18</v>
+        <f>SUM(C20:W20)</f>
+        <v>24</v>
       </c>
       <c r="AB20">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="AC20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD20">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="AE20">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2833,37 +2833,37 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <v>0</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -2872,46 +2872,46 @@
         <v>0</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" cm="1">
         <f t="array" ref="X21">SUM(INDEX(C21:W21, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y21" cm="1">
         <f t="array" ref="Y21">SUM(INDEX(C21:W21, {4,11,12,13,17,19}))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z21" cm="1">
         <f t="array" ref="Z21">SUM(INDEX(C21:W21, {15,16,18,20,21}))</f>
         <v>3</v>
       </c>
       <c r="AA21">
-        <f t="shared" ref="AA21" si="13">SUM(C21:W21)</f>
-        <v>13</v>
+        <f>SUM(C21:W21)</f>
+        <v>3</v>
       </c>
       <c r="AB21">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="AC21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD21">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AE21">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -2932,37 +2932,37 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -2971,46 +2971,46 @@
         <v>0</v>
       </c>
       <c r="V22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" cm="1">
         <f t="array" ref="X22">SUM(INDEX(C22:W22, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y22" cm="1">
         <f t="array" ref="Y22">SUM(INDEX(C22:W22, {4,11,12,13,17,19}))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z22" cm="1">
         <f t="array" ref="Z22">SUM(INDEX(C22:W22, {15,16,18,20,21}))</f>
         <v>3</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f>SUM(C22:W22)</f>
+        <v>13</v>
       </c>
       <c r="AB22">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="AC22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD22">
+        <v>25</v>
+      </c>
+      <c r="AE22">
         <v>18</v>
       </c>
-      <c r="AE22">
-        <v>8</v>
-      </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -3019,25 +3019,25 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>1</v>
@@ -3049,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P23">
         <v>1</v>
@@ -3058,10 +3058,10 @@
         <v>1</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -3070,157 +3070,157 @@
         <v>0</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" cm="1">
         <f t="array" ref="X23">SUM(INDEX(C23:W23, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23" cm="1">
         <f t="array" ref="Y23">SUM(INDEX(C23:W23, {4,11,12,13,17,19}))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z23" cm="1">
         <f t="array" ref="Z23">SUM(INDEX(C23:W23, {15,16,18,20,21}))</f>
+        <v>3</v>
+      </c>
+      <c r="AA23">
+        <f>SUM(C23:W23)</f>
+        <v>18</v>
+      </c>
+      <c r="AB23">
+        <v>30</v>
+      </c>
+      <c r="AC23">
+        <v>2</v>
+      </c>
+      <c r="AD23">
         <v>6</v>
       </c>
-      <c r="AA23">
-        <f t="shared" si="8"/>
-        <v>19</v>
-      </c>
-      <c r="AB23">
-        <v>55</v>
-      </c>
-      <c r="AC23">
-        <v>2</v>
-      </c>
-      <c r="AD23">
-        <v>8</v>
-      </c>
       <c r="AE23">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24">
         <v>2</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X24" cm="1">
         <f t="array" ref="X24">SUM(INDEX(C24:W24, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y24" cm="1">
         <f t="array" ref="Y24">SUM(INDEX(C24:W24, {4,11,12,13,17,19}))</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Z24" cm="1">
         <f t="array" ref="Z24">SUM(INDEX(C24:W24, {15,16,18,20,21}))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA24">
-        <f t="shared" si="8"/>
-        <v>32</v>
+        <f>SUM(C24:W24)</f>
+        <v>41</v>
       </c>
       <c r="AB24">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AC24">
         <v>2</v>
       </c>
       <c r="AD24">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AE24">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3229,40 +3229,40 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L25">
         <v>2</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25">
         <v>1</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25">
         <v>1</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S25">
         <v>2</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U25">
         <v>1</v>
@@ -3275,138 +3275,138 @@
       </c>
       <c r="X25" cm="1">
         <f t="array" ref="X25">SUM(INDEX(C25:W25, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y25" cm="1">
         <f t="array" ref="Y25">SUM(INDEX(C25:W25, {4,11,12,13,17,19}))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z25" cm="1">
         <f t="array" ref="Z25">SUM(INDEX(C25:W25, {15,16,18,20,21}))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA25">
-        <f t="shared" si="8"/>
-        <v>33</v>
+        <f>SUM(C25:W25)</f>
+        <v>30</v>
       </c>
       <c r="AB25">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AC25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD25">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AE25">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26">
         <v>2</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>2</v>
       </c>
       <c r="T26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" cm="1">
         <f t="array" ref="X26">SUM(INDEX(C26:W26, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Y26" cm="1">
         <f t="array" ref="Y26">SUM(INDEX(C26:W26, {4,11,12,13,17,19}))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z26" cm="1">
         <f t="array" ref="Z26">SUM(INDEX(C26:W26, {15,16,18,20,21}))</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA26">
-        <f t="shared" si="8"/>
-        <v>27</v>
+        <f>SUM(C26:W26)</f>
+        <v>32</v>
       </c>
       <c r="AB26">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AC26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD26">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AE26">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -3415,31 +3415,31 @@
         <v>3</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>3</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>3</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N27">
         <v>3</v>
@@ -3448,220 +3448,220 @@
         <v>3</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q27">
         <v>3</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S27">
         <v>3</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X27" cm="1">
         <f t="array" ref="X27">SUM(INDEX(C27:W27, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Y27" cm="1">
         <f t="array" ref="Y27">SUM(INDEX(C27:W27, {4,11,12,13,17,19}))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z27" cm="1">
         <f t="array" ref="Z27">SUM(INDEX(C27:W27, {15,16,18,20,21}))</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AA27">
-        <f t="shared" ref="AA27" si="14">SUM(C27:W27)</f>
-        <v>47</v>
+        <f>SUM(C27:W27)</f>
+        <v>44</v>
       </c>
       <c r="AB27">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="AC27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD27">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AE27">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>3</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S28">
         <v>2</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" cm="1">
         <f t="array" ref="X28">SUM(INDEX(C28:W28, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y28" cm="1">
         <f t="array" ref="Y28">SUM(INDEX(C28:W28, {4,11,12,13,17,19}))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z28" cm="1">
         <f t="array" ref="Z28">SUM(INDEX(C28:W28, {15,16,18,20,21}))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA28">
-        <f t="shared" si="8"/>
+        <f>SUM(C28:W28)</f>
+        <v>38</v>
+      </c>
+      <c r="AB28">
         <v>40</v>
       </c>
-      <c r="AB28">
-        <v>43</v>
-      </c>
       <c r="AC28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD28">
         <v>5</v>
       </c>
       <c r="AE28">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P29">
         <v>1</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29">
         <v>0</v>
       </c>
       <c r="U29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29">
         <v>2</v>
@@ -3671,60 +3671,60 @@
       </c>
       <c r="X29" cm="1">
         <f t="array" ref="X29">SUM(INDEX(C29:W29, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Y29" cm="1">
         <f t="array" ref="Y29">SUM(INDEX(C29:W29, {4,11,12,13,17,19}))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z29" cm="1">
         <f t="array" ref="Z29">SUM(INDEX(C29:W29, {15,16,18,20,21}))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA29">
-        <f t="shared" si="8"/>
-        <v>22</v>
+        <f>SUM(C29:W29)</f>
+        <v>32</v>
       </c>
       <c r="AB29">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AC29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD29">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="AE29">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30">
         <v>3</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -3733,28 +3733,28 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O30">
         <v>2</v>
       </c>
       <c r="P30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30">
         <v>0</v>
@@ -3763,85 +3763,85 @@
         <v>0</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W30">
         <v>3</v>
       </c>
       <c r="X30" cm="1">
         <f t="array" ref="X30">SUM(INDEX(C30:W30, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Y30" cm="1">
         <f t="array" ref="Y30">SUM(INDEX(C30:W30, {4,11,12,13,17,19}))</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z30" cm="1">
         <f t="array" ref="Z30">SUM(INDEX(C30:W30, {15,16,18,20,21}))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA30">
-        <f t="shared" si="8"/>
-        <v>32</v>
+        <f>SUM(C30:W30)</f>
+        <v>30</v>
       </c>
       <c r="AB30">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="AC30">
         <v>2</v>
       </c>
       <c r="AD30">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE30">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>3</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P31">
         <v>1</v>
@@ -3853,7 +3853,7 @@
         <v>3</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T31">
         <v>0</v>
@@ -3862,14 +3862,14 @@
         <v>1</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X31" cm="1">
         <f t="array" ref="X31">SUM(INDEX(C31:W31, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Y31" cm="1">
         <f t="array" ref="Y31">SUM(INDEX(C31:W31, {4,11,12,13,17,19}))</f>
@@ -3877,31 +3877,31 @@
       </c>
       <c r="Z31" cm="1">
         <f t="array" ref="Z31">SUM(INDEX(C31:W31, {15,16,18,20,21}))</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AA31">
-        <f t="shared" si="8"/>
-        <v>35</v>
+        <f>SUM(C31:W31)</f>
+        <v>37</v>
       </c>
       <c r="AB31">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AC31">
         <v>2</v>
       </c>
       <c r="AD31">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE31">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -3910,142 +3910,142 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32">
         <v>1</v>
       </c>
       <c r="M32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32">
         <v>1</v>
       </c>
       <c r="O32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32">
         <v>1</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32">
         <v>2</v>
       </c>
       <c r="V32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X32" cm="1">
         <f t="array" ref="X32">SUM(INDEX(C32:W32, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y32" cm="1">
         <f t="array" ref="Y32">SUM(INDEX(C32:W32, {4,11,12,13,17,19}))</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z32" cm="1">
         <f t="array" ref="Z32">SUM(INDEX(C32:W32, {15,16,18,20,21}))</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA32">
         <f>SUM(C32:W32)</f>
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AB32">
+        <v>39</v>
+      </c>
+      <c r="AC32">
+        <v>1</v>
+      </c>
+      <c r="AD32">
+        <v>1</v>
+      </c>
+      <c r="AE32">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" t="s">
         <v>46</v>
       </c>
-      <c r="AC32">
-        <v>2</v>
-      </c>
-      <c r="AD32">
-        <v>40</v>
-      </c>
-      <c r="AE32">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" t="s">
-        <v>84</v>
-      </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33">
         <v>1</v>
       </c>
       <c r="M33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O33">
         <v>1</v>
       </c>
       <c r="P33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -4057,166 +4057,162 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X33" cm="1">
         <f t="array" ref="X33">SUM(INDEX(C33:W33, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y33" cm="1">
         <f t="array" ref="Y33">SUM(INDEX(C33:W33, {4,11,12,13,17,19}))</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Z33" cm="1">
         <f t="array" ref="Z33">SUM(INDEX(C33:W33, {15,16,18,20,21}))</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA33">
         <f>SUM(C33:W33)</f>
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="AB33">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="AC33">
         <v>2</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE33">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" t="s">
+        <v>50</v>
+      </c>
+      <c r="I34" t="s">
+        <v>50</v>
+      </c>
+      <c r="J34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K34" t="s">
+        <v>50</v>
+      </c>
+      <c r="L34" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" t="s">
+        <v>50</v>
+      </c>
+      <c r="N34" t="s">
+        <v>50</v>
+      </c>
+      <c r="O34" t="s">
+        <v>50</v>
+      </c>
+      <c r="P34" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>50</v>
+      </c>
+      <c r="R34" t="s">
+        <v>50</v>
+      </c>
+      <c r="S34" t="s">
+        <v>50</v>
+      </c>
+      <c r="T34" t="s">
+        <v>50</v>
+      </c>
+      <c r="U34" t="s">
+        <v>50</v>
+      </c>
+      <c r="V34" t="s">
+        <v>50</v>
+      </c>
+      <c r="W34" t="s">
+        <v>50</v>
+      </c>
+      <c r="X34" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB34">
+        <v>46</v>
+      </c>
+      <c r="AC34">
+        <v>2</v>
+      </c>
+      <c r="AD34">
+        <v>15</v>
+      </c>
+      <c r="AE34">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34">
-        <v>3</v>
-      </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>2</v>
-      </c>
-      <c r="G34">
-        <v>3</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>3</v>
-      </c>
-      <c r="J34">
-        <v>2</v>
-      </c>
-      <c r="K34">
-        <v>3</v>
-      </c>
-      <c r="L34">
-        <v>2</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>2</v>
-      </c>
-      <c r="O34">
-        <v>3</v>
-      </c>
-      <c r="P34">
-        <v>1</v>
-      </c>
-      <c r="Q34">
-        <v>2</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>2</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>1</v>
-      </c>
-      <c r="X34" cm="1">
-        <f t="array" ref="X34">SUM(INDEX(C34:W34, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>20</v>
-      </c>
-      <c r="Y34" cm="1">
-        <f t="array" ref="Y34">SUM(INDEX(C34:W34, {4,11,12,13,17,19}))</f>
-        <v>9</v>
-      </c>
-      <c r="Z34" cm="1">
-        <f t="array" ref="Z34">SUM(INDEX(C34:W34, {15,16,18,20,21}))</f>
-        <v>3</v>
-      </c>
-      <c r="AA34">
-        <f>SUM(C34:W34)</f>
-        <v>32</v>
-      </c>
-      <c r="AB34">
-        <v>34</v>
-      </c>
-      <c r="AC34">
-        <v>2</v>
-      </c>
-      <c r="AD34">
-        <v>12</v>
-      </c>
-      <c r="AE34">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>1</v>
@@ -4225,47 +4221,47 @@
         <v>1</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N35">
         <v>1</v>
       </c>
       <c r="O35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P35">
         <v>1</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R35">
         <v>1</v>
       </c>
       <c r="S35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35">
         <v>3</v>
       </c>
       <c r="X35" cm="1">
         <f t="array" ref="X35">SUM(INDEX(C35:W35, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y35" cm="1">
         <f t="array" ref="Y35">SUM(INDEX(C35:W35, {4,11,12,13,17,19}))</f>
@@ -4273,64 +4269,64 @@
       </c>
       <c r="Z35" cm="1">
         <f t="array" ref="Z35">SUM(INDEX(C35:W35, {15,16,18,20,21}))</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AA35">
-        <f t="shared" si="8"/>
-        <v>30</v>
+        <f>SUM(C35:W35)</f>
+        <v>22</v>
       </c>
       <c r="AB35">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="AC35">
         <v>2</v>
       </c>
       <c r="AD35">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE35">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36">
         <v>3</v>
       </c>
       <c r="K36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N36">
         <v>3</v>
@@ -4339,82 +4335,82 @@
         <v>2</v>
       </c>
       <c r="P36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X36" cm="1">
         <f t="array" ref="X36">SUM(INDEX(C36:W36, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="Y36" cm="1">
         <f t="array" ref="Y36">SUM(INDEX(C36:W36, {4,11,12,13,17,19}))</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Z36" cm="1">
         <f t="array" ref="Z36">SUM(INDEX(C36:W36, {15,16,18,20,21}))</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AA36">
-        <f t="shared" si="8"/>
-        <v>32</v>
+        <f>SUM(C36:W36)</f>
+        <v>53</v>
       </c>
       <c r="AB36">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="AC36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE36">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <v>2</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37">
         <v>2</v>
@@ -4429,10 +4425,10 @@
         <v>1</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37">
         <v>1</v>
@@ -4441,13 +4437,13 @@
         <v>1</v>
       </c>
       <c r="Q37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T37">
         <v>0</v>
@@ -4459,157 +4455,157 @@
         <v>1</v>
       </c>
       <c r="W37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X37" cm="1">
         <f t="array" ref="X37">SUM(INDEX(C37:W37, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y37" cm="1">
         <f t="array" ref="Y37">SUM(INDEX(C37:W37, {4,11,12,13,17,19}))</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z37" cm="1">
         <f t="array" ref="Z37">SUM(INDEX(C37:W37, {15,16,18,20,21}))</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AA37">
-        <f t="shared" si="8"/>
-        <v>37</v>
+        <f>SUM(C37:W37)</f>
+        <v>27</v>
       </c>
       <c r="AB37">
+        <v>34</v>
+      </c>
+      <c r="AC37">
+        <v>2</v>
+      </c>
+      <c r="AD37">
+        <v>13</v>
+      </c>
+      <c r="AE37">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>45</v>
       </c>
-      <c r="AC37">
-        <v>2</v>
-      </c>
-      <c r="AD37">
-        <v>16</v>
-      </c>
-      <c r="AE37">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>44</v>
-      </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G38">
         <v>2</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S38">
         <v>1</v>
       </c>
       <c r="T38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X38" cm="1">
         <f t="array" ref="X38">SUM(INDEX(C38:W38, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Y38" cm="1">
         <f t="array" ref="Y38">SUM(INDEX(C38:W38, {4,11,12,13,17,19}))</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Z38" cm="1">
         <f t="array" ref="Z38">SUM(INDEX(C38:W38, {15,16,18,20,21}))</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AA38">
         <f>SUM(C38:W38)</f>
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AB38">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AC38">
         <v>1</v>
       </c>
       <c r="AD38">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="AE38">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -4621,327 +4617,331 @@
         <v>1</v>
       </c>
       <c r="K39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T39">
         <v>0</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" cm="1">
         <f t="array" ref="X39">SUM(INDEX(C39:W39, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y39" cm="1">
         <f t="array" ref="Y39">SUM(INDEX(C39:W39, {4,11,12,13,17,19}))</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Z39" cm="1">
         <f t="array" ref="Z39">SUM(INDEX(C39:W39, {15,16,18,20,21}))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA39">
         <f>SUM(C39:W39)</f>
+        <v>10</v>
+      </c>
+      <c r="AB39">
         <v>23</v>
       </c>
-      <c r="AB39">
-        <v>37</v>
-      </c>
       <c r="AC39">
         <v>2</v>
       </c>
       <c r="AD39">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AE39">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O40">
         <v>2</v>
       </c>
       <c r="P40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q40">
         <v>3</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40">
         <v>1</v>
       </c>
       <c r="W40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X40" cm="1">
         <f t="array" ref="X40">SUM(INDEX(C40:W40, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="Y40" cm="1">
         <f t="array" ref="Y40">SUM(INDEX(C40:W40, {4,11,12,13,17,19}))</f>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Z40" cm="1">
         <f t="array" ref="Z40">SUM(INDEX(C40:W40, {15,16,18,20,21}))</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AA40">
-        <f t="shared" ref="AA40" si="15">SUM(C40:W40)</f>
-        <v>53</v>
+        <f>SUM(C40:W40)</f>
+        <v>25</v>
       </c>
       <c r="AB40">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="AC40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD40">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE40">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" t="s">
-        <v>50</v>
-      </c>
-      <c r="F41" t="s">
-        <v>50</v>
-      </c>
-      <c r="G41" t="s">
-        <v>50</v>
-      </c>
-      <c r="H41" t="s">
-        <v>50</v>
-      </c>
-      <c r="I41" t="s">
-        <v>50</v>
-      </c>
-      <c r="J41" t="s">
-        <v>50</v>
-      </c>
-      <c r="K41" t="s">
-        <v>50</v>
-      </c>
-      <c r="L41" t="s">
-        <v>50</v>
-      </c>
-      <c r="M41" t="s">
-        <v>50</v>
-      </c>
-      <c r="N41" t="s">
-        <v>50</v>
-      </c>
-      <c r="O41" t="s">
-        <v>50</v>
-      </c>
-      <c r="P41" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>50</v>
-      </c>
-      <c r="R41" t="s">
-        <v>50</v>
-      </c>
-      <c r="S41" t="s">
-        <v>50</v>
-      </c>
-      <c r="T41" t="s">
-        <v>50</v>
-      </c>
-      <c r="U41" t="s">
-        <v>50</v>
-      </c>
-      <c r="V41" t="s">
-        <v>50</v>
-      </c>
-      <c r="W41" t="s">
-        <v>50</v>
-      </c>
-      <c r="X41" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA41" t="s">
-        <v>50</v>
+        <v>107</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>2</v>
+      </c>
+      <c r="N41">
+        <v>2</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>2</v>
+      </c>
+      <c r="Q41">
+        <v>1</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>2</v>
+      </c>
+      <c r="V41">
+        <v>2</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41" cm="1">
+        <f t="array" ref="X41">SUM(INDEX(C41:W41, {1,2,3,5,6,7,8,9,10,14}))</f>
+        <v>13</v>
+      </c>
+      <c r="Y41" cm="1">
+        <f t="array" ref="Y41">SUM(INDEX(C41:W41, {4,11,12,13,17,19}))</f>
+        <v>8</v>
+      </c>
+      <c r="Z41" cm="1">
+        <f t="array" ref="Z41">SUM(INDEX(C41:W41, {15,16,18,20,21}))</f>
+        <v>4</v>
+      </c>
+      <c r="AA41">
+        <f>SUM(C41:W41)</f>
+        <v>25</v>
       </c>
       <c r="AB41">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AC41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD41">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AE41">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S42">
         <v>1</v>
       </c>
       <c r="T42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -4950,137 +4950,140 @@
         <v>3</v>
       </c>
       <c r="W42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X42" cm="1">
         <f t="array" ref="X42">SUM(INDEX(C42:W42, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y42" cm="1">
         <f t="array" ref="Y42">SUM(INDEX(C42:W42, {4,11,12,13,17,19}))</f>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Z42" cm="1">
         <f t="array" ref="Z42">SUM(INDEX(C42:W42, {15,16,18,20,21}))</f>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA42">
         <f>SUM(C42:W42)</f>
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="AB42">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AC42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD42">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE42">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R43">
         <v>1</v>
       </c>
       <c r="S43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U43">
         <v>0</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" cm="1">
         <f t="array" ref="X43">SUM(INDEX(C43:W43, {1,2,3,5,6,7,8,9,10,14}))</f>
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="Y43" cm="1">
         <f t="array" ref="Y43">SUM(INDEX(C43:W43, {4,11,12,13,17,19}))</f>
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Z43" cm="1">
         <f t="array" ref="Z43">SUM(INDEX(C43:W43, {15,16,18,20,21}))</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AA43">
         <f>SUM(C43:W43)</f>
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AB43">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="AC43">
         <v>2</v>
       </c>
       <c r="AD43">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AE43">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AE43">
+    <sortCondition ref="A1:A43"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5088,9 +5091,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C53C76-FF94-D249-AA9A-6F4764C599CE}">
   <dimension ref="A1:AE14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -5173,7 +5176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -5260,7 +5263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -5347,7 +5350,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -5434,7 +5437,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -5521,7 +5524,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -5608,7 +5611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -5695,7 +5698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -5782,7 +5785,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -5869,7 +5872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -5956,7 +5959,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -6055,7 +6058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -6142,7 +6145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -6229,7 +6232,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -6324,9 +6327,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5961F868-A238-EA43-87E5-9D82D76CAD00}">
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -6409,7 +6412,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -6502,7 +6505,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -6595,7 +6598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -6688,7 +6691,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -6781,7 +6784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -6874,7 +6877,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -6967,7 +6970,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -7060,7 +7063,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -7153,7 +7156,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -7236,7 +7239,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -7329,7 +7332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -7422,7 +7425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -7515,7 +7518,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -7608,7 +7611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="21:21" x14ac:dyDescent="0.3">
       <c r="U18" t="s">
         <v>141</v>
       </c>
@@ -7621,9 +7624,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA394A0-E846-1341-BEEC-C2F40712C84E}">
   <dimension ref="A1:AA14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -7706,7 +7709,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -7799,7 +7802,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -7892,7 +7895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -7985,7 +7988,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -8078,7 +8081,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -8171,7 +8174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -8264,7 +8267,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -8357,7 +8360,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -8450,7 +8453,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -8543,7 +8546,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -8636,7 +8639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -8729,7 +8732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -8822,7 +8825,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>88</v>
       </c>

--- a/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
+++ b/data/raw/BDI_ThreeFactor_MultiSubject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9860f92a834cae8/Belgeler/GitHub/FrequencySliding/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaankeskin/projects/FrequencySliding/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{AFC6E653-CF34-5542-98C6-1F68F9130B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9BDA4F7-6514-4765-ACD9-8C18711D139F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DD9BCD-137F-0B41-B65D-DD80FAD501EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19280" yWindow="660" windowWidth="18980" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BDI-II Multi" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="152">
   <si>
     <t>SubjectID</t>
   </si>
@@ -484,16 +484,53 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>EzgiBarış</t>
+  </si>
+  <si>
+    <t>sub-43</t>
+  </si>
+  <si>
+    <t>MuhammedGaziKölgelikaya</t>
+  </si>
+  <si>
+    <t>sub-44</t>
+  </si>
+  <si>
+    <t>BurcuAyTemel</t>
+  </si>
+  <si>
+    <t>sub-45</t>
+  </si>
+  <si>
+    <t>MedihaBuluter</t>
+  </si>
+  <si>
+    <t>sub-46</t>
+  </si>
+  <si>
+    <t>KenanUludağ</t>
+  </si>
+  <si>
+    <t>sub-47</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -519,8 +556,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -825,13 +863,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE43"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE48"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -926,7 +964,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1009,7 +1047,7 @@
         <v>10</v>
       </c>
       <c r="AA2">
-        <f>SUM(C2:W2)</f>
+        <f t="shared" ref="AA2:AA33" si="0">SUM(C2:W2)</f>
         <v>33</v>
       </c>
       <c r="AB2">
@@ -1025,7 +1063,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -1108,7 +1146,7 @@
         <v>6</v>
       </c>
       <c r="AA3">
-        <f>SUM(C3:W3)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="AB3">
@@ -1124,7 +1162,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -1207,7 +1245,7 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <f>SUM(C4:W4)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="AB4">
@@ -1223,7 +1261,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1306,7 +1344,7 @@
         <v>7</v>
       </c>
       <c r="AA5">
-        <f>SUM(C5:W5)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="AB5">
@@ -1322,7 +1360,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -1405,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="AA6">
-        <f>SUM(C6:W6)</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="AB6">
@@ -1421,7 +1459,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -1504,7 +1542,7 @@
         <v>3</v>
       </c>
       <c r="AA7">
-        <f>SUM(C7:W7)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="AB7">
@@ -1520,7 +1558,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -1603,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="AA8">
-        <f>SUM(C8:W8)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="AB8">
@@ -1619,7 +1657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1702,7 +1740,7 @@
         <v>3</v>
       </c>
       <c r="AA9">
-        <f>SUM(C9:W9)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AB9">
@@ -1718,7 +1756,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>90</v>
       </c>
@@ -1801,7 +1839,7 @@
         <v>6</v>
       </c>
       <c r="AA10">
-        <f>SUM(C10:W10)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="AB10">
@@ -1817,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -1900,7 +1938,7 @@
         <v>6</v>
       </c>
       <c r="AA11">
-        <f>SUM(C11:W11)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="AB11">
@@ -1916,7 +1954,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -1999,7 +2037,7 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <f>SUM(C12:W12)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="AB12">
@@ -2015,7 +2053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -2098,7 +2136,7 @@
         <v>11</v>
       </c>
       <c r="AA13">
-        <f>SUM(C13:W13)</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="AB13">
@@ -2114,7 +2152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>98</v>
       </c>
@@ -2197,7 +2235,7 @@
         <v>9</v>
       </c>
       <c r="AA14">
-        <f>SUM(C14:W14)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="AB14">
@@ -2213,7 +2251,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -2296,7 +2334,7 @@
         <v>8</v>
       </c>
       <c r="AA15">
-        <f>SUM(C15:W15)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="AB15">
@@ -2312,7 +2350,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -2395,7 +2433,7 @@
         <v>12</v>
       </c>
       <c r="AA16">
-        <f>SUM(C16:W16)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="AB16">
@@ -2411,7 +2449,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>100</v>
       </c>
@@ -2494,7 +2532,7 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <f>SUM(C17:W17)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="AB17">
@@ -2510,7 +2548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -2593,7 +2631,7 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <f>SUM(C18:W18)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="AB18">
@@ -2609,7 +2647,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -2692,7 +2730,7 @@
         <v>14</v>
       </c>
       <c r="AA19">
-        <f>SUM(C19:W19)</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="AB19">
@@ -2708,7 +2746,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -2791,7 +2829,7 @@
         <v>4</v>
       </c>
       <c r="AA20">
-        <f>SUM(C20:W20)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="AB20">
@@ -2807,7 +2845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -2890,7 +2928,7 @@
         <v>3</v>
       </c>
       <c r="AA21">
-        <f>SUM(C21:W21)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="AB21">
@@ -2906,7 +2944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>110</v>
       </c>
@@ -2989,7 +3027,7 @@
         <v>3</v>
       </c>
       <c r="AA22">
-        <f>SUM(C22:W22)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="AB22">
@@ -3005,7 +3043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>108</v>
       </c>
@@ -3088,7 +3126,7 @@
         <v>3</v>
       </c>
       <c r="AA23">
-        <f>SUM(C23:W23)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="AB23">
@@ -3104,7 +3142,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -3187,7 +3225,7 @@
         <v>7</v>
       </c>
       <c r="AA24">
-        <f>SUM(C24:W24)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="AB24">
@@ -3203,7 +3241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -3286,7 +3324,7 @@
         <v>9</v>
       </c>
       <c r="AA25">
-        <f>SUM(C25:W25)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="AB25">
@@ -3302,7 +3340,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -3385,7 +3423,7 @@
         <v>3</v>
       </c>
       <c r="AA26">
-        <f>SUM(C26:W26)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="AB26">
@@ -3401,7 +3439,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -3484,7 +3522,7 @@
         <v>13</v>
       </c>
       <c r="AA27">
-        <f>SUM(C27:W27)</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="AB27">
@@ -3500,7 +3538,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -3583,7 +3621,7 @@
         <v>6</v>
       </c>
       <c r="AA28">
-        <f>SUM(C28:W28)</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="AB28">
@@ -3599,7 +3637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -3682,7 +3720,7 @@
         <v>6</v>
       </c>
       <c r="AA29">
-        <f>SUM(C29:W29)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="AB29">
@@ -3698,7 +3736,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>75</v>
       </c>
@@ -3781,7 +3819,7 @@
         <v>6</v>
       </c>
       <c r="AA30">
-        <f>SUM(C30:W30)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="AB30">
@@ -3797,7 +3835,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -3880,7 +3918,7 @@
         <v>9</v>
       </c>
       <c r="AA31">
-        <f>SUM(C31:W31)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="AB31">
@@ -3896,7 +3934,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -3979,7 +4017,7 @@
         <v>3</v>
       </c>
       <c r="AA32">
-        <f>SUM(C32:W32)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AB32">
@@ -3995,7 +4033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>87</v>
       </c>
@@ -4078,7 +4116,7 @@
         <v>4</v>
       </c>
       <c r="AA33">
-        <f>SUM(C33:W33)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="AB33">
@@ -4094,7 +4132,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -4189,7 +4227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>102</v>
       </c>
@@ -4272,7 +4310,7 @@
         <v>4</v>
       </c>
       <c r="AA35">
-        <f>SUM(C35:W35)</f>
+        <f t="shared" ref="AA35:AA43" si="1">SUM(C35:W35)</f>
         <v>22</v>
       </c>
       <c r="AB35">
@@ -4288,7 +4326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -4371,7 +4409,7 @@
         <v>11</v>
       </c>
       <c r="AA36">
-        <f>SUM(C36:W36)</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="AB36">
@@ -4387,7 +4425,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -4470,7 +4508,7 @@
         <v>4</v>
       </c>
       <c r="AA37">
-        <f>SUM(C37:W37)</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="AB37">
@@ -4486,7 +4524,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -4569,7 +4607,7 @@
         <v>14</v>
       </c>
       <c r="AA38">
-        <f>SUM(C38:W38)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="AB38">
@@ -4585,7 +4623,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -4668,7 +4706,7 @@
         <v>2</v>
       </c>
       <c r="AA39">
-        <f>SUM(C39:W39)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="AB39">
@@ -4684,7 +4722,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>104</v>
       </c>
@@ -4767,7 +4805,7 @@
         <v>6</v>
       </c>
       <c r="AA40">
-        <f>SUM(C40:W40)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="AB40">
@@ -4783,7 +4821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>106</v>
       </c>
@@ -4866,7 +4904,7 @@
         <v>4</v>
       </c>
       <c r="AA41">
-        <f>SUM(C41:W41)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="AB41">
@@ -4882,7 +4920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -4965,7 +5003,7 @@
         <v>4</v>
       </c>
       <c r="AA42">
-        <f>SUM(C42:W42)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="AB42">
@@ -4981,7 +5019,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>62</v>
       </c>
@@ -5064,7 +5102,7 @@
         <v>11</v>
       </c>
       <c r="AA43">
-        <f>SUM(C43:W43)</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="AB43">
@@ -5077,6 +5115,481 @@
         <v>5</v>
       </c>
       <c r="AE43">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2</v>
+      </c>
+      <c r="D44" s="1">
+        <v>3</v>
+      </c>
+      <c r="E44" s="1">
+        <v>3</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>3</v>
+      </c>
+      <c r="H44" s="1">
+        <v>3</v>
+      </c>
+      <c r="I44" s="1">
+        <v>3</v>
+      </c>
+      <c r="J44" s="1">
+        <v>3</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>2</v>
+      </c>
+      <c r="M44" s="1">
+        <v>1</v>
+      </c>
+      <c r="N44" s="1">
+        <v>2</v>
+      </c>
+      <c r="O44" s="1">
+        <v>1</v>
+      </c>
+      <c r="P44" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>3</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>2</v>
+      </c>
+      <c r="T44" s="1">
+        <v>2</v>
+      </c>
+      <c r="U44" s="1">
+        <v>1</v>
+      </c>
+      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1">
+        <v>3</v>
+      </c>
+      <c r="X44" s="1">
+        <v>25</v>
+      </c>
+      <c r="Y44" s="1">
+        <v>8</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>8</v>
+      </c>
+      <c r="AA44" s="1">
+        <v>41</v>
+      </c>
+      <c r="AB44" s="1">
+        <v>27</v>
+      </c>
+      <c r="AC44" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD44" s="1">
+        <v>15</v>
+      </c>
+      <c r="AE44" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C45" s="1">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1">
+        <v>3</v>
+      </c>
+      <c r="G45" s="1">
+        <v>3</v>
+      </c>
+      <c r="H45" s="1">
+        <v>2</v>
+      </c>
+      <c r="I45" s="1">
+        <v>3</v>
+      </c>
+      <c r="J45" s="1">
+        <v>3</v>
+      </c>
+      <c r="K45" s="1">
+        <v>3</v>
+      </c>
+      <c r="L45" s="1">
+        <v>3</v>
+      </c>
+      <c r="M45" s="1">
+        <v>3</v>
+      </c>
+      <c r="N45" s="1">
+        <v>3</v>
+      </c>
+      <c r="O45" s="1">
+        <v>3</v>
+      </c>
+      <c r="P45" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>3</v>
+      </c>
+      <c r="R45" s="1">
+        <v>1</v>
+      </c>
+      <c r="S45" s="1">
+        <v>3</v>
+      </c>
+      <c r="T45" s="1">
+        <v>0</v>
+      </c>
+      <c r="U45" s="1">
+        <v>0</v>
+      </c>
+      <c r="V45" s="1">
+        <v>1</v>
+      </c>
+      <c r="W45" s="1">
+        <v>1</v>
+      </c>
+      <c r="X45" s="1">
+        <v>28</v>
+      </c>
+      <c r="Y45" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z45" s="1">
+        <v>6</v>
+      </c>
+      <c r="AA45" s="1">
+        <v>49</v>
+      </c>
+      <c r="AB45" s="1">
+        <v>21</v>
+      </c>
+      <c r="AC45" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD45" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE45" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" s="1">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1">
+        <v>2</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>2</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>2</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1">
+        <v>3</v>
+      </c>
+      <c r="N46" s="1">
+        <v>3</v>
+      </c>
+      <c r="O46" s="1">
+        <v>2</v>
+      </c>
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>3</v>
+      </c>
+      <c r="R46" s="1">
+        <v>3</v>
+      </c>
+      <c r="S46" s="1">
+        <v>3</v>
+      </c>
+      <c r="T46" s="1">
+        <v>2</v>
+      </c>
+      <c r="U46" s="1">
+        <v>2</v>
+      </c>
+      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="W46" s="1">
+        <v>3</v>
+      </c>
+      <c r="X46" s="1">
+        <v>15</v>
+      </c>
+      <c r="Y46" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z46" s="1">
+        <v>11</v>
+      </c>
+      <c r="AA46" s="1">
+        <v>41</v>
+      </c>
+      <c r="AB46">
+        <v>37</v>
+      </c>
+      <c r="AC46" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD46" s="1">
+        <v>25</v>
+      </c>
+      <c r="AE46" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" s="1">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
+      <c r="F47" s="1">
+        <v>3</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>1</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1">
+        <v>2</v>
+      </c>
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>3</v>
+      </c>
+      <c r="R47" s="1">
+        <v>1</v>
+      </c>
+      <c r="S47" s="1">
+        <v>3</v>
+      </c>
+      <c r="T47" s="1">
+        <v>0</v>
+      </c>
+      <c r="U47" s="1">
+        <v>0</v>
+      </c>
+      <c r="V47" s="1">
+        <v>3</v>
+      </c>
+      <c r="W47" s="1">
+        <v>1</v>
+      </c>
+      <c r="X47" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="1">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="1">
+        <v>8</v>
+      </c>
+      <c r="AA47" s="1">
+        <v>21</v>
+      </c>
+      <c r="AB47" s="1">
+        <v>45</v>
+      </c>
+      <c r="AC47" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD47" s="1">
+        <v>20</v>
+      </c>
+      <c r="AE47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1">
+        <v>2</v>
+      </c>
+      <c r="F48" s="1">
+        <v>2</v>
+      </c>
+      <c r="G48" s="1">
+        <v>3</v>
+      </c>
+      <c r="H48" s="1">
+        <v>3</v>
+      </c>
+      <c r="I48" s="1">
+        <v>2</v>
+      </c>
+      <c r="J48" s="1">
+        <v>3</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1</v>
+      </c>
+      <c r="M48" s="1">
+        <v>3</v>
+      </c>
+      <c r="N48" s="1">
+        <v>2</v>
+      </c>
+      <c r="O48" s="1">
+        <v>2</v>
+      </c>
+      <c r="P48" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>3</v>
+      </c>
+      <c r="R48" s="1">
+        <v>2</v>
+      </c>
+      <c r="S48" s="1">
+        <v>1</v>
+      </c>
+      <c r="T48" s="1">
+        <v>2</v>
+      </c>
+      <c r="U48" s="1">
+        <v>2</v>
+      </c>
+      <c r="V48" s="1">
+        <v>0</v>
+      </c>
+      <c r="W48" s="1">
+        <v>2</v>
+      </c>
+      <c r="X48" s="1">
+        <v>18</v>
+      </c>
+      <c r="Y48" s="1">
+        <v>12</v>
+      </c>
+      <c r="Z48" s="1">
+        <v>9</v>
+      </c>
+      <c r="AA48" s="1">
+        <v>39</v>
+      </c>
+      <c r="AB48" s="1">
+        <v>52</v>
+      </c>
+      <c r="AC48" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD48" s="1">
+        <v>10</v>
+      </c>
+      <c r="AE48" s="1">
         <v>12</v>
       </c>
     </row>
@@ -5091,9 +5604,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C53C76-FF94-D249-AA9A-6F4764C599CE}">
   <dimension ref="A1:AE14"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -5176,7 +5689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -5263,7 +5776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -5350,7 +5863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -5437,7 +5950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -5524,7 +6037,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -5611,7 +6124,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -5698,7 +6211,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -5785,7 +6298,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -5872,7 +6385,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -5959,7 +6472,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -6058,7 +6571,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -6145,7 +6658,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -6232,7 +6745,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -6327,9 +6840,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5961F868-A238-EA43-87E5-9D82D76CAD00}">
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -6412,7 +6925,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -6505,7 +7018,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -6598,7 +7111,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -6691,7 +7204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -6784,7 +7297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -6877,7 +7390,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -6970,7 +7483,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -7063,7 +7576,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -7156,7 +7669,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -7239,7 +7752,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -7332,7 +7845,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -7425,7 +7938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -7518,7 +8031,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -7611,7 +8124,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="21:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="21:21" x14ac:dyDescent="0.2">
       <c r="U18" t="s">
         <v>141</v>
       </c>
@@ -7624,9 +8137,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA394A0-E846-1341-BEEC-C2F40712C84E}">
   <dimension ref="A1:AA14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -7709,7 +8222,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -7802,7 +8315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -7895,7 +8408,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -7988,7 +8501,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -8081,7 +8594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -8174,7 +8687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -8267,7 +8780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -8360,7 +8873,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -8453,7 +8966,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -8546,7 +9059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -8639,7 +9152,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -8732,7 +9245,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -8825,7 +9338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>88</v>
       </c>
